--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C7828F-BE12-4306-85A1-2D7E090245F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28D0B2C9-A0CA-4735-84D9-84E790155737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -850,18 +850,36 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_003</t>
   </si>
   <si>
@@ -886,30 +904,18 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_019</t>
   </si>
   <si>
@@ -922,22 +928,46 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_017</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_solelc_spv_001</t>
@@ -946,42 +976,21 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w166838338-400,e_w191352746-220,e_PL62-400,e_w198635989-220,e_w170368942-220</t>
+  </si>
+  <si>
+    <t>e_w121656686-220,e_w121656686-400,e_w255972326-400,e_w303870256-400,e_PL17-400,e_w293489663-400,e_w170259740-220</t>
+  </si>
+  <si>
+    <t>e_w303870256-400,e_w170259740-220</t>
+  </si>
+  <si>
     <t>e_PL18-400,e_PL10-400,e_PL4-220,e_w668348943-220,e_w385539724-220,e_PL8-220</t>
   </si>
   <si>
@@ -997,63 +1006,138 @@
     <t>e_w255972397-400,e_PL27-400,e_PL17-400,e_w194903381-400,e_w293489663-400</t>
   </si>
   <si>
-    <t>e_w166838338-400,e_w191352746-220,e_PL62-400,e_w198635989-220,e_w170368942-220</t>
-  </si>
-  <si>
-    <t>e_w121656686-220,e_w121656686-400,e_w255972326-400,e_w303870256-400,e_PL17-400,e_w293489663-400,e_w170259740-220</t>
-  </si>
-  <si>
-    <t>e_w303870256-400,e_w170259740-220</t>
-  </si>
-  <si>
     <t>e_w177749653-220,e_w179279860-220,e_w336990960-220,e_w255277953-400</t>
   </si>
   <si>
+    <t>e_w175406958-220,e_w175406958-400,e_w178838661-220,e_w255314292,e_w534238983-400,e_r18085709-400</t>
+  </si>
+  <si>
     <t>e_w199098050-220,e_w145037309-220,e_w228154083-220,e_w189851841-220,e_PL32-220</t>
   </si>
   <si>
     <t>e_w726776987-220,e_w170368942-220,e_w148060965-400,e_w173613665-220,e_w194903381-400</t>
   </si>
   <si>
+    <t>e_w145037309-220,e_w29115701-220,e_w91384044-400,e_PL20-220</t>
+  </si>
+  <si>
+    <t>e_w254235846-400,e_w173582810-400,e_w255973806-220,e_w88544449-220,e_w255972397-400</t>
+  </si>
+  <si>
     <t>e_PL22-220,e_PL15-400,e_w72879943-220,e_w143484238-220,e_w658600169-400,e_w144646702-400</t>
   </si>
   <si>
-    <t>e_w145037309-220,e_w29115701-220,e_w91384044-400,e_PL20-220</t>
-  </si>
-  <si>
-    <t>e_w254235846-400,e_w173582810-400,e_w255973806-220,e_w88544449-220,e_w255972397-400</t>
+    <t>e_w180535363-220,e_w32036484-220,e_w238640596-220,e_w175406958-220,e_w32036484-400,e_w238640596-400,e_w254938713-400,e_w255293400-220</t>
+  </si>
+  <si>
+    <t>e_w255293400-220,e_w46235456-400,e_w385118244-400,e_w46092396-400,e_PL3-220,e_w112614319-400,e_PL6-220</t>
+  </si>
+  <si>
+    <t>e_w185459155-220,e_w336990960-220,e_PL36-400,e_w184899160-220,e_w293489607-400,e_PL41-400,e_w171917072-400,e_w241842600-400,e_PL35-220,e_w199098050-220</t>
+  </si>
+  <si>
+    <t>e_w255293403-400,e_w255284259-220,e_w171383831-220,e_w35366436-220,e_PL21-220</t>
   </si>
   <si>
     <t>e_PL40-220,e_w158232924-220,e_w178756295-220,e_w111615226-400,e_PL30-220</t>
   </si>
   <si>
-    <t>e_w175406958-220,e_w175406958-400,e_w178838661-220,e_w255314292,e_w534238983-400,e_r18085709-400</t>
-  </si>
-  <si>
-    <t>e_w180535363-220,e_w32036484-220,e_w238640596-220,e_w175406958-220,e_w32036484-400,e_w238640596-400,e_w254938713-400,e_w255293400-220</t>
-  </si>
-  <si>
-    <t>e_w255293400-220,e_w46235456-400,e_w385118244-400,e_w46092396-400,e_PL3-220,e_w112614319-400,e_PL6-220</t>
-  </si>
-  <si>
-    <t>e_w185459155-220,e_w336990960-220,e_PL36-400,e_w184899160-220,e_w293489607-400,e_PL41-400,e_w171917072-400,e_w241842600-400,e_PL35-220,e_w199098050-220</t>
-  </si>
-  <si>
-    <t>e_w255293403-400,e_w255284259-220,e_w171383831-220,e_w35366436-220,e_PL21-220</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_013</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_016</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_010</t>
   </si>
   <si>
@@ -1078,102 +1162,99 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_won_013</t>
   </si>
   <si>
     <t>e_w180542657-220,e_w180535363-220,e_w154510504-400,e_w148197330-220,e_w79033485-400,e_w255293403-400</t>
   </si>
   <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220,e_w111615226-400</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220,e_w66051759-220,e_w241842600-400,e_w115801644-220,e_w87667718-220,e_w199098050-220</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220,e_w144646702-400,e_w101914781-220,e_w91384044-400,e_PL24-220,e_w101915790-220</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220,e_w98611253-220,e_w115801644-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w101914781-220,e_w101914781-400,e_w101915790-220,e_w303870256-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220,e_PL18-400,e_PL10-400,e_PL30-220,e_w385539724-220</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220,e_w177749653-220,e_w179279860-220,e_PL46-220,e_w336990960-220,e_w255277953-400,e_PL36-400</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220,e_w32036484-220,e_w238640596-220,e_w32036484-400,e_w254938713-400,e_w255293400-220</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400,e_w255284259-220,e_PL22-220,e_PL15-400,e_w171383831-220,e_w72879943-220,e_w143484238-220,e_PL21-220,e_w658600169-400,e_w144646702-400</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220,e_w228154083-220,e_w189851841-220,e_w191352746-220,e_w254235846-400,e_w173582810-400,e_w726776987-220,e_w88544449-220</t>
+  </si>
+  <si>
     <t>elc_won_016</t>
   </si>
   <si>
     <t>e_PL62-400,e_w198635989-220</t>
   </si>
   <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220,e_w121656686-400,e_w255972326-400,e_w303870256-400,e_w170259740-220,e_PL17-400,e_w293489663-400,e_w194903381-400</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400,e_w46092396-400,e_PL3-220,e_w112614319-400,e_PL6-220</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w166710856-400,e_w166838338-400</t>
+  </si>
+  <si>
     <t>elc_won_010</t>
   </si>
   <si>
@@ -1198,87 +1279,6 @@
     <t>e_w255973806-220,e_PL20-220,e_w88544449-220,e_w255972397-400,e_w148060965-400,e_PL27-400,e_PL17-400</t>
   </si>
   <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220,e_PL18-400,e_PL10-400,e_PL30-220,e_w385539724-220</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220,e_w177749653-220,e_w179279860-220,e_PL46-220,e_w336990960-220,e_w255277953-400,e_PL36-400</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220,e_w32036484-220,e_w238640596-220,e_w32036484-400,e_w254938713-400,e_w255293400-220</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400,e_w255284259-220,e_PL22-220,e_PL15-400,e_w171383831-220,e_w72879943-220,e_w143484238-220,e_PL21-220,e_w658600169-400,e_w144646702-400</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220,e_w228154083-220,e_w189851841-220,e_w191352746-220,e_w254235846-400,e_w173582810-400,e_w726776987-220,e_w88544449-220</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220,e_w66051759-220,e_w241842600-400,e_w115801644-220,e_w87667718-220,e_w199098050-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220,e_w144646702-400,e_w101914781-220,e_w91384044-400,e_PL24-220,e_w101915790-220</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220,e_w98611253-220,e_w115801644-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w166710856-400,e_w166838338-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220,e_w121656686-400,e_w255972326-400,e_w303870256-400,e_w170259740-220,e_PL17-400,e_w293489663-400,e_w194903381-400</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w101914781-220,e_w101914781-400,e_w101915790-220,e_w303870256-400</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220,e_w111615226-400</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400,e_w46092396-400,e_PL3-220,e_w112614319-400,e_PL6-220</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
@@ -1297,6 +1297,30 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
@@ -1309,36 +1333,12 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
@@ -1357,6 +1357,30 @@
     <t>e_w112614319-400</t>
   </si>
   <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w255314292,e_PL1-400</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w86494356-400,e_w112614319-400</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w175406958-220,e_w175406958-400</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_PL1-400</t>
+  </si>
+  <si>
     <t>elc_wof_005</t>
   </si>
   <si>
@@ -1369,31 +1393,7 @@
     <t>e_w175406958-400,e_w255314292</t>
   </si>
   <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w175406958-220,e_w175406958-400</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_PL1-400</t>
-  </si>
-  <si>
     <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w255314292,e_PL1-400</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w86494356-400,e_w112614319-400</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7131,7 +7131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C584D4-2F0C-4DE1-B5E8-D274BA1C8475}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9002CCA-3A41-4B3C-ADAD-94C0F766DF0E}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7369,16 +7369,16 @@
         <v>240</v>
       </c>
       <c r="Y11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="Z11" t="s">
         <v>284</v>
       </c>
       <c r="AA11">
-        <v>0.99795567063794977</v>
+        <v>0.99510129733839103</v>
       </c>
       <c r="AB11">
-        <v>37.479371637587086</v>
+        <v>89.80954879616533</v>
       </c>
       <c r="AD11" t="s">
         <v>239</v>
@@ -7515,16 +7515,16 @@
         <v>244</v>
       </c>
       <c r="Y12" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="Z12" t="s">
         <v>285</v>
       </c>
       <c r="AA12">
-        <v>0.99842917020202115</v>
+        <v>0.9969465945713758</v>
       </c>
       <c r="AB12">
-        <v>28.79854629627873</v>
+        <v>55.979099524777816</v>
       </c>
       <c r="AD12" t="s">
         <v>239</v>
@@ -7557,10 +7557,10 @@
         <v>347</v>
       </c>
       <c r="AO12">
-        <v>0.9948929932931313</v>
+        <v>0.99799398386987059</v>
       </c>
       <c r="AP12">
-        <v>93.628456292592972</v>
+        <v>36.776962385706796</v>
       </c>
       <c r="AR12" t="s">
         <v>239</v>
@@ -7661,16 +7661,16 @@
         <v>246</v>
       </c>
       <c r="Y13" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Z13" t="s">
         <v>286</v>
       </c>
       <c r="AA13">
-        <v>0.99803521994530153</v>
+        <v>0.99510522570170612</v>
       </c>
       <c r="AB13">
-        <v>36.020967669471958</v>
+        <v>89.737528802053845</v>
       </c>
       <c r="AD13" t="s">
         <v>239</v>
@@ -7703,10 +7703,10 @@
         <v>349</v>
       </c>
       <c r="AO13">
-        <v>0.99764612849471446</v>
+        <v>0.99874397974028573</v>
       </c>
       <c r="AP13">
-        <v>43.154310930234999</v>
+        <v>23.027038094760776</v>
       </c>
       <c r="AR13" t="s">
         <v>239</v>
@@ -7807,16 +7807,16 @@
         <v>248</v>
       </c>
       <c r="Y14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z14" t="s">
         <v>287</v>
       </c>
       <c r="AA14">
-        <v>0.99641682822356314</v>
+        <v>0.99795567063794977</v>
       </c>
       <c r="AB14">
-        <v>65.691482568009889</v>
+        <v>37.479371637587086</v>
       </c>
       <c r="AD14" t="s">
         <v>239</v>
@@ -7849,10 +7849,10 @@
         <v>351</v>
       </c>
       <c r="AO14">
-        <v>0.9984109444597864</v>
+        <v>0.99650928369028746</v>
       </c>
       <c r="AP14">
-        <v>29.132684903915262</v>
+        <v>63.996465678063821</v>
       </c>
       <c r="AR14" t="s">
         <v>239</v>
@@ -7885,10 +7885,10 @@
         <v>410</v>
       </c>
       <c r="BC14">
-        <v>0.9932866968373224</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD14">
-        <v>123.07722464908932</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7953,16 +7953,16 @@
         <v>250</v>
       </c>
       <c r="Y15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z15" t="s">
         <v>288</v>
       </c>
       <c r="AA15">
-        <v>0.99576711713325516</v>
+        <v>0.99842917020202115</v>
       </c>
       <c r="AB15">
-        <v>77.602852556989035</v>
+        <v>28.79854629627873</v>
       </c>
       <c r="AD15" t="s">
         <v>239</v>
@@ -7995,10 +7995,10 @@
         <v>353</v>
       </c>
       <c r="AO15">
-        <v>0.99877589632587693</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP15">
-        <v>22.441900692257164</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR15" t="s">
         <v>239</v>
@@ -8031,10 +8031,10 @@
         <v>412</v>
       </c>
       <c r="BC15">
-        <v>0.99399718012600935</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD15">
-        <v>110.05169768982766</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8099,16 +8099,16 @@
         <v>252</v>
       </c>
       <c r="Y16" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z16" t="s">
         <v>289</v>
       </c>
       <c r="AA16">
-        <v>0.99510129733839103</v>
+        <v>0.99803521994530153</v>
       </c>
       <c r="AB16">
-        <v>89.80954879616533</v>
+        <v>36.020967669471958</v>
       </c>
       <c r="AD16" t="s">
         <v>239</v>
@@ -8141,10 +8141,10 @@
         <v>355</v>
       </c>
       <c r="AO16">
-        <v>0.99793052663183923</v>
+        <v>0.99532032875047627</v>
       </c>
       <c r="AP16">
-        <v>37.940345082946791</v>
+        <v>85.793972907934105</v>
       </c>
       <c r="AR16" t="s">
         <v>239</v>
@@ -8245,16 +8245,16 @@
         <v>254</v>
       </c>
       <c r="Y17" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="Z17" t="s">
         <v>290</v>
       </c>
       <c r="AA17">
-        <v>0.9969465945713758</v>
+        <v>0.99641682822356314</v>
       </c>
       <c r="AB17">
-        <v>55.979099524777816</v>
+        <v>65.691482568009889</v>
       </c>
       <c r="AD17" t="s">
         <v>239</v>
@@ -8391,16 +8391,16 @@
         <v>256</v>
       </c>
       <c r="Y18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z18" t="s">
         <v>291</v>
       </c>
       <c r="AA18">
-        <v>0.99510522570170612</v>
+        <v>0.99576711713325516</v>
       </c>
       <c r="AB18">
-        <v>89.737528802053845</v>
+        <v>77.602852556989035</v>
       </c>
       <c r="AD18" t="s">
         <v>239</v>
@@ -8466,13 +8466,13 @@
         <v>417</v>
       </c>
       <c r="BB18" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="BC18">
-        <v>0.99564789206089888</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD18">
-        <v>79.788645550187297</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8609,16 +8609,16 @@
         <v>399</v>
       </c>
       <c r="BA19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="BB19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="BC19">
-        <v>0.99255696761939116</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD19">
-        <v>136.4555936444961</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8683,16 +8683,16 @@
         <v>260</v>
       </c>
       <c r="Y20" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="Z20" t="s">
         <v>293</v>
       </c>
       <c r="AA20">
-        <v>0.99776747864513293</v>
+        <v>0.99787294196585663</v>
       </c>
       <c r="AB20">
-        <v>40.929558172561954</v>
+        <v>38.996063959294339</v>
       </c>
       <c r="AD20" t="s">
         <v>239</v>
@@ -8755,16 +8755,16 @@
         <v>401</v>
       </c>
       <c r="BA20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="BB20" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="BC20">
-        <v>0.99353710926584593</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD20">
-        <v>118.48633012615811</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8829,16 +8829,16 @@
         <v>262</v>
       </c>
       <c r="Y21" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Z21" t="s">
         <v>294</v>
       </c>
       <c r="AA21">
-        <v>0.99629609186318691</v>
+        <v>0.99776747864513293</v>
       </c>
       <c r="AB21">
-        <v>67.904982508241062</v>
+        <v>40.929558172561954</v>
       </c>
       <c r="AD21" t="s">
         <v>239</v>
@@ -8939,16 +8939,16 @@
         <v>264</v>
       </c>
       <c r="Y22" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Z22" t="s">
         <v>295</v>
       </c>
       <c r="AA22">
-        <v>0.99834414580432929</v>
+        <v>0.99629609186318691</v>
       </c>
       <c r="AB22">
-        <v>30.357326920630218</v>
+        <v>67.904982508241062</v>
       </c>
       <c r="AD22" t="s">
         <v>239</v>
@@ -8981,10 +8981,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99874397974028573</v>
+        <v>0.9948929932931313</v>
       </c>
       <c r="AP22">
-        <v>23.027038094760776</v>
+        <v>93.628456292592972</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9091,10 +9091,10 @@
         <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99650928369028746</v>
+        <v>0.99625753626847613</v>
       </c>
       <c r="AP23">
-        <v>63.996465678063821</v>
+        <v>68.61183507793757</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9201,10 +9201,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99641308487583879</v>
+        <v>0.99701344658679592</v>
       </c>
       <c r="AP24">
-        <v>65.760110609622657</v>
+        <v>54.753479242075251</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9269,16 +9269,16 @@
         <v>270</v>
       </c>
       <c r="Y25" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="Z25" t="s">
         <v>298</v>
       </c>
       <c r="AA25">
-        <v>0.99739570149600498</v>
+        <v>0.99834414580432929</v>
       </c>
       <c r="AB25">
-        <v>47.74547257324172</v>
+        <v>30.357326920630218</v>
       </c>
       <c r="AD25" t="s">
         <v>239</v>
@@ -9308,13 +9308,13 @@
         <v>372</v>
       </c>
       <c r="AN25" t="s">
-        <v>373</v>
+        <v>295</v>
       </c>
       <c r="AO25">
-        <v>0.99776911581804295</v>
+        <v>0.99594655953670175</v>
       </c>
       <c r="AP25">
-        <v>40.899543335879912</v>
+        <v>74.313075160468429</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9379,16 +9379,16 @@
         <v>272</v>
       </c>
       <c r="Y26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z26" t="s">
         <v>299</v>
       </c>
       <c r="AA26">
-        <v>0.99787294196585663</v>
+        <v>0.9973099707215185</v>
       </c>
       <c r="AB26">
-        <v>38.996063959294339</v>
+        <v>49.317203438826922</v>
       </c>
       <c r="AD26" t="s">
         <v>239</v>
@@ -9415,16 +9415,16 @@
         <v>334</v>
       </c>
       <c r="AM26" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN26" t="s">
         <v>374</v>
       </c>
-      <c r="AN26" t="s">
-        <v>375</v>
-      </c>
       <c r="AO26">
-        <v>0.99625753626847613</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP26">
-        <v>68.61183507793757</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9489,16 +9489,16 @@
         <v>274</v>
       </c>
       <c r="Y27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Z27" t="s">
         <v>300</v>
       </c>
       <c r="AA27">
-        <v>0.9973099707215185</v>
+        <v>0.997251448551293</v>
       </c>
       <c r="AB27">
-        <v>49.317203438826922</v>
+        <v>50.39010989296083</v>
       </c>
       <c r="AD27" t="s">
         <v>239</v>
@@ -9525,16 +9525,16 @@
         <v>336</v>
       </c>
       <c r="AM27" t="s">
+        <v>375</v>
+      </c>
+      <c r="AN27" t="s">
         <v>376</v>
       </c>
-      <c r="AN27" t="s">
-        <v>377</v>
-      </c>
       <c r="AO27">
-        <v>0.99532032875047627</v>
+        <v>0.99764612849471446</v>
       </c>
       <c r="AP27">
-        <v>85.793972907934105</v>
+        <v>43.154310930234999</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9599,16 +9599,16 @@
         <v>276</v>
       </c>
       <c r="Y28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="Z28" t="s">
         <v>301</v>
       </c>
       <c r="AA28">
-        <v>0.997251448551293</v>
+        <v>0.99859778038316893</v>
       </c>
       <c r="AB28">
-        <v>50.39010989296083</v>
+        <v>25.707359641902851</v>
       </c>
       <c r="AD28" t="s">
         <v>239</v>
@@ -9635,16 +9635,16 @@
         <v>338</v>
       </c>
       <c r="AM28" t="s">
+        <v>377</v>
+      </c>
+      <c r="AN28" t="s">
         <v>378</v>
       </c>
-      <c r="AN28" t="s">
-        <v>379</v>
-      </c>
       <c r="AO28">
-        <v>0.99799398386987059</v>
+        <v>0.9984109444597864</v>
       </c>
       <c r="AP28">
-        <v>36.776962385706796</v>
+        <v>29.132684903915262</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9709,16 +9709,16 @@
         <v>278</v>
       </c>
       <c r="Y29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z29" t="s">
         <v>302</v>
       </c>
       <c r="AA29">
-        <v>0.99859778038316893</v>
+        <v>0.99828081140420921</v>
       </c>
       <c r="AB29">
-        <v>25.707359641902851</v>
+        <v>31.518457589497565</v>
       </c>
       <c r="AD29" t="s">
         <v>239</v>
@@ -9745,16 +9745,16 @@
         <v>340</v>
       </c>
       <c r="AM29" t="s">
+        <v>379</v>
+      </c>
+      <c r="AN29" t="s">
         <v>380</v>
       </c>
-      <c r="AN29" t="s">
-        <v>381</v>
-      </c>
       <c r="AO29">
-        <v>0.99701344658679592</v>
+        <v>0.99877589632587693</v>
       </c>
       <c r="AP29">
-        <v>54.753479242075251</v>
+        <v>22.441900692257164</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9819,16 +9819,16 @@
         <v>280</v>
       </c>
       <c r="Y30" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="Z30" t="s">
         <v>303</v>
       </c>
       <c r="AA30">
-        <v>0.99828081140420921</v>
+        <v>0.99739570149600498</v>
       </c>
       <c r="AB30">
-        <v>31.518457589497565</v>
+        <v>47.74547257324172</v>
       </c>
       <c r="AD30" t="s">
         <v>239</v>
@@ -9855,16 +9855,16 @@
         <v>342</v>
       </c>
       <c r="AM30" t="s">
+        <v>381</v>
+      </c>
+      <c r="AN30" t="s">
         <v>382</v>
       </c>
-      <c r="AN30" t="s">
-        <v>294</v>
-      </c>
       <c r="AO30">
-        <v>0.99594655953670175</v>
+        <v>0.99793052663183923</v>
       </c>
       <c r="AP30">
-        <v>74.313075160468429</v>
+        <v>37.940345082946791</v>
       </c>
     </row>
   </sheetData>
@@ -9873,7 +9873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207BF338-D9B3-43A6-A079-8792B48FAF0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629BF7DD-CDC8-4BA5-A051-A84BCEF4DDA7}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9985,7 +9985,7 @@
         <v>422</v>
       </c>
       <c r="K11" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="L11">
         <v>0.45167200935612223</v>
@@ -10086,7 +10086,7 @@
         <v>464</v>
       </c>
       <c r="X12" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10121,7 +10121,7 @@
         <v>426</v>
       </c>
       <c r="K13" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="L13">
         <v>1.7897871713950226</v>
@@ -10154,7 +10154,7 @@
         <v>466</v>
       </c>
       <c r="X13" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10189,7 +10189,7 @@
         <v>428</v>
       </c>
       <c r="K14" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="L14">
         <v>2.6804732670444085</v>
@@ -10222,7 +10222,7 @@
         <v>468</v>
       </c>
       <c r="X14" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10257,7 +10257,7 @@
         <v>430</v>
       </c>
       <c r="K15" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L15">
         <v>8.0517810049421517</v>
@@ -10290,7 +10290,7 @@
         <v>470</v>
       </c>
       <c r="X15" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10393,7 +10393,7 @@
         <v>434</v>
       </c>
       <c r="K17" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="L17">
         <v>1.093890418371007</v>
@@ -10461,7 +10461,7 @@
         <v>436</v>
       </c>
       <c r="K18" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="L18">
         <v>3.1665724666245323</v>
@@ -10529,7 +10529,7 @@
         <v>438</v>
       </c>
       <c r="K19" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="L19">
         <v>0.55491188155257321</v>
@@ -10562,7 +10562,7 @@
         <v>478</v>
       </c>
       <c r="X19" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10597,7 +10597,7 @@
         <v>440</v>
       </c>
       <c r="K20" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="L20">
         <v>0.97886072674627833</v>
@@ -10665,7 +10665,7 @@
         <v>442</v>
       </c>
       <c r="K21" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="L21">
         <v>0.40593208719379742</v>
@@ -10805,7 +10805,7 @@
         <v>450</v>
       </c>
       <c r="K25" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10840,7 +10840,7 @@
         <v>452</v>
       </c>
       <c r="K26" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="L26">
         <v>0.89446396558783758</v>
@@ -10875,7 +10875,7 @@
         <v>454</v>
       </c>
       <c r="K27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10945,7 +10945,7 @@
         <v>458</v>
       </c>
       <c r="K29" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="L29">
         <v>0.63042801517356961</v>
@@ -10980,7 +10980,7 @@
         <v>460</v>
       </c>
       <c r="K30" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="L30">
         <v>0.61343702722931326</v>
@@ -10995,7 +10995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5558CF-6C83-4ED1-9442-DE842E5034AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DEBF5B-31FE-4816-9A29-254671B25B73}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12812,7 +12812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCE3AF4-8499-494B-8939-9559BB0C5939}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF53A26D-06EC-4773-956A-1CE503C0FAB8}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E6054AD-643A-47F9-A848-4C46E8E51ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84D72793-F362-489C-B31F-A006CC209029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,120 +853,120 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_014</t>
   </si>
   <si>
@@ -985,66 +985,144 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
+  </si>
+  <si>
+    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
+  </si>
+  <si>
     <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
   </si>
   <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
-  </si>
-  <si>
-    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
-  </si>
-  <si>
-    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
-  </si>
-  <si>
     <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
   </si>
   <si>
     <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_013</t>
   </si>
   <si>
@@ -1057,112 +1135,109 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_007</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
@@ -1177,109 +1252,82 @@
     <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
     <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_004</t>
@@ -1294,52 +1342,49 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL,e_w255314292_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -1352,51 +1397,6 @@
   </si>
   <si>
     <t>e_PL1-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL,e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7139,7 +7139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F782CD9-0405-4E16-8969-D8D116399AAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22FA35C-609C-4580-A310-625E3A83D1FC}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7377,16 +7377,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99729953359766199</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB11">
-        <v>49.508550709529651</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -7419,10 +7419,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99883902037019667</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP11">
-        <v>21.284626546395259</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7455,10 +7455,10 @@
         <v>405</v>
       </c>
       <c r="BC11">
-        <v>0.99255696761939116</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD11">
-        <v>136.4555936444961</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7523,16 +7523,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99692898913090644</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB12">
-        <v>56.301865933381954</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -7565,10 +7565,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99521984547821263</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP12">
-        <v>87.636166232768815</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7601,10 +7601,10 @@
         <v>407</v>
       </c>
       <c r="BC12">
-        <v>0.99615776238359954</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD12">
-        <v>70.441022967342263</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7669,16 +7669,16 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.99738245649758195</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB13">
-        <v>47.988297544331637</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
@@ -7711,10 +7711,10 @@
         <v>350</v>
       </c>
       <c r="AO13">
-        <v>0.99653588726932718</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP13">
-        <v>63.508733395668145</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7747,10 +7747,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.99399718012600935</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD13">
-        <v>110.05169768982766</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7815,16 +7815,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99505524223378883</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB14">
-        <v>90.653892380538664</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7857,10 +7857,10 @@
         <v>352</v>
       </c>
       <c r="AO14">
-        <v>0.99641308487583879</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP14">
-        <v>65.760110609622657</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7893,10 +7893,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99609037037675463</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD14">
-        <v>71.676543092831025</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7961,16 +7961,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99763459325217896</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB15">
-        <v>43.365790376719588</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -8000,13 +8000,13 @@
         <v>353</v>
       </c>
       <c r="AN15" t="s">
-        <v>354</v>
+        <v>297</v>
       </c>
       <c r="AO15">
-        <v>0.99449756685866841</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP15">
-        <v>100.87794092441324</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8039,10 +8039,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99353710926584593</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD15">
-        <v>118.48633012615811</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8107,16 +8107,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99511607748745434</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB16">
-        <v>89.538579396670116</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8143,16 +8143,16 @@
         <v>315</v>
       </c>
       <c r="AM16" t="s">
+        <v>354</v>
+      </c>
+      <c r="AN16" t="s">
         <v>355</v>
       </c>
-      <c r="AN16" t="s">
-        <v>356</v>
-      </c>
       <c r="AO16">
-        <v>0.99845079995590791</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP16">
-        <v>28.402000808355538</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8185,10 +8185,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99603343715055259</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD16">
-        <v>72.720318906536249</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8289,16 +8289,16 @@
         <v>317</v>
       </c>
       <c r="AM17" t="s">
+        <v>356</v>
+      </c>
+      <c r="AN17" t="s">
         <v>357</v>
       </c>
-      <c r="AN17" t="s">
-        <v>358</v>
-      </c>
       <c r="AO17">
-        <v>0.9963019969989696</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP17">
-        <v>67.796721685557472</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8331,10 +8331,10 @@
         <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.9932866968373224</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD17">
-        <v>123.07722464908932</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8435,16 +8435,16 @@
         <v>319</v>
       </c>
       <c r="AM18" t="s">
+        <v>358</v>
+      </c>
+      <c r="AN18" t="s">
         <v>359</v>
       </c>
-      <c r="AN18" t="s">
-        <v>360</v>
-      </c>
       <c r="AO18">
-        <v>0.99635146162488653</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP18">
-        <v>66.889870210414614</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8474,13 +8474,13 @@
         <v>418</v>
       </c>
       <c r="BB18" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="BC18">
-        <v>0.99644388872049838</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD18">
-        <v>65.195373457529499</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8581,16 +8581,16 @@
         <v>321</v>
       </c>
       <c r="AM19" t="s">
+        <v>360</v>
+      </c>
+      <c r="AN19" t="s">
         <v>361</v>
       </c>
-      <c r="AN19" t="s">
-        <v>301</v>
-      </c>
       <c r="AO19">
-        <v>0.99586212495478665</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP19">
-        <v>75.861042495577635</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8617,16 +8617,16 @@
         <v>400</v>
       </c>
       <c r="BA19" t="s">
+        <v>419</v>
+      </c>
+      <c r="BB19" t="s">
         <v>420</v>
       </c>
-      <c r="BB19" t="s">
-        <v>421</v>
-      </c>
       <c r="BC19">
-        <v>0.99383395234396599</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD19">
-        <v>113.04420702728957</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8691,16 +8691,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99860106452186825</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB20">
-        <v>25.647150432415483</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8733,10 +8733,10 @@
         <v>363</v>
       </c>
       <c r="AO20">
-        <v>0.99802303154782224</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP20">
-        <v>36.244421623259619</v>
+        <v>28.402000808355538</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8763,16 +8763,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
+        <v>421</v>
+      </c>
+      <c r="BB20" t="s">
         <v>422</v>
       </c>
-      <c r="BB20" t="s">
-        <v>419</v>
-      </c>
       <c r="BC20">
-        <v>0.99564789206089888</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD20">
-        <v>79.788645550187297</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8837,16 +8837,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99775856069920277</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB21">
-        <v>41.093053847949164</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8879,10 +8879,10 @@
         <v>365</v>
       </c>
       <c r="AO21">
-        <v>0.99714358927215652</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP21">
-        <v>52.367530010463909</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8947,16 +8947,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99812712894455979</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB22">
-        <v>34.335969349736395</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -8989,10 +8989,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99826576737141715</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP22">
-        <v>31.794264857351436</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99834158364926728</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB23">
-        <v>30.404299763434018</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9099,10 +9099,10 @@
         <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99871360797890252</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP23">
-        <v>23.583853720120768</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9167,16 +9167,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.9987403722896917</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB24">
-        <v>23.093174688985375</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9209,10 +9209,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99873239758997023</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP24">
-        <v>23.239377517213022</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9277,16 +9277,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99839233674974392</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB25">
-        <v>29.473826254695162</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -9319,10 +9319,10 @@
         <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.99730422320290779</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP25">
-        <v>49.422574613357185</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9387,16 +9387,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99648087644372252</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB26">
-        <v>64.517265198419722</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9429,10 +9429,10 @@
         <v>375</v>
       </c>
       <c r="AO26">
-        <v>0.99805709209211746</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP26">
-        <v>35.619978311179104</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9497,16 +9497,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99621535905375425</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB27">
-        <v>69.385084014505708</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9539,10 +9539,10 @@
         <v>377</v>
       </c>
       <c r="AO27">
-        <v>0.99622969699231045</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP27">
-        <v>69.122221807641537</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9607,16 +9607,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99572127940552169</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB28">
-        <v>78.443210898768598</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9649,10 +9649,10 @@
         <v>379</v>
       </c>
       <c r="AO28">
-        <v>0.99749126227646956</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP28">
-        <v>45.993524931390482</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9759,10 +9759,10 @@
         <v>381</v>
       </c>
       <c r="AO29">
-        <v>0.99807543246352515</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP29">
-        <v>35.283738168705199</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9869,10 +9869,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99776911581804295</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP30">
-        <v>40.899543335879912</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
   </sheetData>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156F3FCD-AA59-4AED-B83E-E543D162A4A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8B558-ACC8-4766-8744-80530948B3E8}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9993,7 +9993,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10026,7 +10026,7 @@
         <v>463</v>
       </c>
       <c r="X11" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10061,7 +10061,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10094,7 +10094,7 @@
         <v>465</v>
       </c>
       <c r="X12" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10129,7 +10129,7 @@
         <v>427</v>
       </c>
       <c r="K13" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10162,7 +10162,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10197,7 +10197,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10230,7 +10230,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10265,7 +10265,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10298,7 +10298,7 @@
         <v>471</v>
       </c>
       <c r="X15" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10333,7 +10333,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10366,7 +10366,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10401,7 +10401,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10434,7 +10434,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10469,7 +10469,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10502,7 +10502,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10537,7 +10537,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10570,7 +10570,7 @@
         <v>479</v>
       </c>
       <c r="X19" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10605,7 +10605,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10638,7 +10638,7 @@
         <v>481</v>
       </c>
       <c r="X20" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10673,7 +10673,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10708,7 +10708,7 @@
         <v>445</v>
       </c>
       <c r="K22" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10743,7 +10743,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10778,7 +10778,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10813,7 +10813,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10848,7 +10848,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10883,7 +10883,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10918,7 +10918,7 @@
         <v>457</v>
       </c>
       <c r="K28" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10953,7 +10953,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -10988,7 +10988,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11003,7 +11003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4D5CFB-28C2-45B7-9A86-5D27B253C3DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DAA072-C0C0-4D38-9DF5-FA94994D0A39}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12820,7 +12820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A11923A-6945-436C-A4FF-A80C30AF467F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A65BD2-A677-4F48-B18E-DB6C342F5210}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13893,7 +13893,7 @@
         <v>569</v>
       </c>
       <c r="C36" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D36" t="s">
         <v>570</v>
@@ -13928,7 +13928,7 @@
         <v>570</v>
       </c>
       <c r="D37" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E37">
         <v>1</v>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84D72793-F362-489C-B31F-A006CC209029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C3D98A-2677-44C3-9076-4ABC8CC16B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,18 +853,54 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_003</t>
   </si>
   <si>
@@ -883,16 +919,10 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_001</t>
@@ -919,10 +949,16 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_006</t>
@@ -937,54 +973,36 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
     <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
   </si>
   <si>
@@ -997,10 +1015,7 @@
     <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
   </si>
   <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
   </si>
   <si>
     <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
@@ -1015,7 +1030,10 @@
     <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
   </si>
   <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
   </si>
   <si>
     <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
@@ -1024,25 +1042,55 @@
     <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
   </si>
   <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
     <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
   </si>
   <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_019</t>
@@ -1051,6 +1099,60 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_014</t>
   </si>
   <si>
@@ -1063,106 +1165,52 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
@@ -1171,6 +1219,57 @@
     <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
@@ -1183,103 +1282,28 @@
     <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_010</t>
@@ -1294,18 +1318,6 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_007</t>
   </si>
   <si>
@@ -1330,16 +1342,28 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_w255314292_POL,e_PL1-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
@@ -1354,18 +1378,6 @@
     <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
@@ -1385,18 +1397,6 @@
   </si>
   <si>
     <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL,e_PL1-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7139,7 +7139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22FA35C-609C-4580-A310-625E3A83D1FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE0A111-D174-4B47-9E57-3F7FED4CC2C1}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7377,16 +7377,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99812712894455979</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB11">
-        <v>34.335969349736395</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -7419,10 +7419,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99873239758997023</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP11">
-        <v>23.239377517213022</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7455,10 +7455,10 @@
         <v>405</v>
       </c>
       <c r="BC11">
-        <v>0.99609037037675463</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD11">
-        <v>71.676543092831025</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7523,16 +7523,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99834158364926728</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB12">
-        <v>30.404299763434018</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -7565,10 +7565,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99730422320290779</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP12">
-        <v>49.422574613357185</v>
+        <v>28.402000808355538</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7601,10 +7601,10 @@
         <v>407</v>
       </c>
       <c r="BC12">
-        <v>0.99353710926584593</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD12">
-        <v>118.48633012615811</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7669,16 +7669,16 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.9987403722896917</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB13">
-        <v>23.093174688985375</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
@@ -7711,10 +7711,10 @@
         <v>350</v>
       </c>
       <c r="AO13">
-        <v>0.99805709209211746</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP13">
-        <v>35.619978311179104</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7747,10 +7747,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.9932866968373224</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD13">
-        <v>123.07722464908932</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7815,16 +7815,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99692898913090644</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB14">
-        <v>56.301865933381954</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7857,10 +7857,10 @@
         <v>352</v>
       </c>
       <c r="AO14">
-        <v>0.99635146162488653</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP14">
-        <v>66.889870210414614</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7893,10 +7893,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99644388872049838</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD14">
-        <v>65.195373457529499</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7961,16 +7961,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99860106452186825</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB15">
-        <v>25.647150432415483</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -8000,13 +8000,13 @@
         <v>353</v>
       </c>
       <c r="AN15" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="AO15">
-        <v>0.99586212495478665</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP15">
-        <v>75.861042495577635</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8039,10 +8039,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99603343715055259</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD15">
-        <v>72.720318906536249</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8107,16 +8107,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99775856069920277</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB16">
-        <v>41.093053847949164</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8143,16 +8143,16 @@
         <v>315</v>
       </c>
       <c r="AM16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO16">
-        <v>0.99749126227646956</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP16">
-        <v>45.993524931390482</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8185,10 +8185,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99399718012600935</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD16">
-        <v>110.05169768982766</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8253,16 +8253,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99733507264559695</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB17">
-        <v>48.857001497390002</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -8289,16 +8289,16 @@
         <v>317</v>
       </c>
       <c r="AM17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO17">
-        <v>0.99807543246352515</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP17">
-        <v>35.283738168705199</v>
+        <v>36.244421623259619</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8331,10 +8331,10 @@
         <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.99383395234396599</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD17">
-        <v>113.04420702728957</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8399,16 +8399,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.99583365539385327</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB18">
-        <v>76.382984446022675</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -8435,16 +8435,16 @@
         <v>319</v>
       </c>
       <c r="AM18" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO18">
-        <v>0.99641308487583879</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP18">
-        <v>65.760110609622657</v>
+        <v>52.367530010463909</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8474,13 +8474,13 @@
         <v>418</v>
       </c>
       <c r="BB18" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="BC18">
-        <v>0.99564789206089888</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD18">
-        <v>79.788645550187297</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8545,16 +8545,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99875154162789404</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB19">
-        <v>22.888403488609324</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -8581,16 +8581,16 @@
         <v>321</v>
       </c>
       <c r="AM19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO19">
-        <v>0.99449756685866841</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP19">
-        <v>100.87794092441324</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8617,16 +8617,16 @@
         <v>400</v>
       </c>
       <c r="BA19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="BB19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="BC19">
-        <v>0.99255696761939116</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD19">
-        <v>136.4555936444961</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8691,16 +8691,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99511607748745434</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB20">
-        <v>89.538579396670116</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8727,16 +8727,16 @@
         <v>323</v>
       </c>
       <c r="AM20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO20">
-        <v>0.99845079995590791</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP20">
-        <v>28.402000808355538</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8763,16 +8763,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="BB20" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="BC20">
-        <v>0.99615776238359954</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD20">
-        <v>70.441022967342263</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8837,16 +8837,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99839233674974392</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB21">
-        <v>29.473826254695162</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8873,16 +8873,16 @@
         <v>325</v>
       </c>
       <c r="AM21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN21" t="s">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="AO21">
-        <v>0.9963019969989696</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP21">
-        <v>67.796721685557472</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8947,16 +8947,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99648087644372252</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB22">
-        <v>64.517265198419722</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -8989,10 +8989,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99622969699231045</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP22">
-        <v>69.122221807641537</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99621535905375425</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB23">
-        <v>69.385084014505708</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9099,10 +9099,10 @@
         <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99776911581804295</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP23">
-        <v>40.899543335879912</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9167,16 +9167,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99572127940552169</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB24">
-        <v>78.443210898768598</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9209,10 +9209,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99883902037019667</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP24">
-        <v>21.284626546395259</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9277,16 +9277,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99738245649758195</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB25">
-        <v>47.988297544331637</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -9319,10 +9319,10 @@
         <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.99521984547821263</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP25">
-        <v>87.636166232768815</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9387,16 +9387,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99505524223378883</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB26">
-        <v>90.653892380538664</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9429,10 +9429,10 @@
         <v>375</v>
       </c>
       <c r="AO26">
-        <v>0.99802303154782224</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP26">
-        <v>36.244421623259619</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9497,16 +9497,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99763459325217896</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB27">
-        <v>43.365790376719588</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9539,10 +9539,10 @@
         <v>377</v>
       </c>
       <c r="AO27">
-        <v>0.99714358927215652</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP27">
-        <v>52.367530010463909</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9607,16 +9607,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99729953359766199</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB28">
-        <v>49.508550709529651</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9649,10 +9649,10 @@
         <v>379</v>
       </c>
       <c r="AO28">
-        <v>0.99826576737141715</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP28">
-        <v>31.794264857351436</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9717,16 +9717,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99801094175818605</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB29">
-        <v>36.466067766588218</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -9759,10 +9759,10 @@
         <v>381</v>
       </c>
       <c r="AO29">
-        <v>0.99871360797890252</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP29">
-        <v>23.583853720120768</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9827,16 +9827,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Z30" t="s">
         <v>304</v>
       </c>
       <c r="AA30">
-        <v>0.99909366739195871</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB30">
-        <v>16.616097814091063</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9869,10 +9869,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99653588726932718</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP30">
-        <v>63.508733395668145</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
   </sheetData>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C8B558-ACC8-4766-8744-80530948B3E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99CF94F9-980A-4CC9-92C4-1C50D2769BEA}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9993,7 +9993,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10026,7 +10026,7 @@
         <v>463</v>
       </c>
       <c r="X11" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10061,7 +10061,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10094,7 +10094,7 @@
         <v>465</v>
       </c>
       <c r="X12" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10129,7 +10129,7 @@
         <v>427</v>
       </c>
       <c r="K13" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10162,7 +10162,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10197,7 +10197,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10230,7 +10230,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10265,7 +10265,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10298,7 +10298,7 @@
         <v>471</v>
       </c>
       <c r="X15" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10333,7 +10333,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10366,7 +10366,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10401,7 +10401,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10434,7 +10434,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10469,7 +10469,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10502,7 +10502,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10537,7 +10537,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10570,7 +10570,7 @@
         <v>479</v>
       </c>
       <c r="X19" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10605,7 +10605,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10638,7 +10638,7 @@
         <v>481</v>
       </c>
       <c r="X20" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10673,7 +10673,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10708,7 +10708,7 @@
         <v>445</v>
       </c>
       <c r="K22" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10743,7 +10743,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10778,7 +10778,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10813,7 +10813,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10848,7 +10848,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10883,7 +10883,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10918,7 +10918,7 @@
         <v>457</v>
       </c>
       <c r="K28" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10953,7 +10953,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -10988,7 +10988,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11003,7 +11003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DAA072-C0C0-4D38-9DF5-FA94994D0A39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F72E12E-1A85-4261-B68C-4C3BEFDBAF61}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12820,7 +12820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A65BD2-A677-4F48-B18E-DB6C342F5210}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2274994D-E095-49EF-8675-1E4F48780984}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13893,7 +13893,7 @@
         <v>569</v>
       </c>
       <c r="C36" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D36" t="s">
         <v>570</v>
@@ -13928,7 +13928,7 @@
         <v>570</v>
       </c>
       <c r="D37" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E37">
         <v>1</v>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C3D98A-2677-44C3-9076-4ABC8CC16B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{109A05B6-BF7E-43BE-89CD-13025D7262E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,28 +853,94 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_019</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_005</t>
@@ -883,40 +949,28 @@
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_007</t>
@@ -925,124 +979,160 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
     <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
   </si>
   <si>
     <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
   </si>
   <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
+  </si>
+  <si>
+    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
   </si>
   <si>
     <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
   </si>
   <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
+  </si>
+  <si>
+    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
   </si>
   <si>
     <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
   </si>
   <si>
-    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
-  </si>
-  <si>
-    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
-  </si>
-  <si>
-    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_017</t>
@@ -1063,12 +1153,6 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_015</t>
   </si>
   <si>
@@ -1081,88 +1165,91 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
@@ -1183,12 +1270,6 @@
     <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
@@ -1201,87 +1282,6 @@
     <t>e_PL62-400_POL,e_w198635989-220_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_005</t>
   </si>
   <si>
@@ -1294,6 +1294,12 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
@@ -1306,6 +1312,24 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_010</t>
   </si>
   <si>
@@ -1318,30 +1342,6 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
@@ -1354,6 +1354,12 @@
     <t>e_w112614319-400_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL,e_w255314292_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
@@ -1366,6 +1372,21 @@
     <t>e_PL1-400_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
@@ -1376,27 +1397,6 @@
   </si>
   <si>
     <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL,e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7139,7 +7139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE0A111-D174-4B47-9E57-3F7FED4CC2C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E44AC0-D54D-4022-A9FC-B37923D62612}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7377,16 +7377,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99860106452186825</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB11">
-        <v>25.647150432415483</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -7419,10 +7419,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99776911581804295</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP11">
-        <v>40.899543335879912</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7523,16 +7523,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99775856069920277</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB12">
-        <v>41.093053847949164</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -7565,10 +7565,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99845079995590791</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP12">
-        <v>28.402000808355538</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7711,10 +7711,10 @@
         <v>350</v>
       </c>
       <c r="AO13">
-        <v>0.9963019969989696</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP13">
-        <v>67.796721685557472</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7747,10 +7747,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.99255696761939116</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD13">
-        <v>136.4555936444961</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7815,16 +7815,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99729953359766199</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB14">
-        <v>49.508550709529651</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7854,13 +7854,13 @@
         <v>351</v>
       </c>
       <c r="AN14" t="s">
-        <v>352</v>
+        <v>297</v>
       </c>
       <c r="AO14">
-        <v>0.99622969699231045</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP14">
-        <v>69.122221807641537</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7893,10 +7893,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99615776238359954</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD14">
-        <v>70.441022967342263</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7961,16 +7961,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99839233674974392</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB15">
-        <v>29.473826254695162</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -7997,16 +7997,16 @@
         <v>313</v>
       </c>
       <c r="AM15" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN15" t="s">
         <v>353</v>
       </c>
-      <c r="AN15" t="s">
-        <v>354</v>
-      </c>
       <c r="AO15">
-        <v>0.99641308487583879</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP15">
-        <v>65.760110609622657</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8039,10 +8039,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99609037037675463</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD15">
-        <v>71.676543092831025</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8107,16 +8107,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99738245649758195</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB16">
-        <v>47.988297544331637</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8143,16 +8143,16 @@
         <v>315</v>
       </c>
       <c r="AM16" t="s">
+        <v>354</v>
+      </c>
+      <c r="AN16" t="s">
         <v>355</v>
       </c>
-      <c r="AN16" t="s">
-        <v>356</v>
-      </c>
       <c r="AO16">
-        <v>0.99449756685866841</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP16">
-        <v>100.87794092441324</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8185,10 +8185,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99353710926584593</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD16">
-        <v>118.48633012615811</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8253,16 +8253,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99812712894455979</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB17">
-        <v>34.335969349736395</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -8289,16 +8289,16 @@
         <v>317</v>
       </c>
       <c r="AM17" t="s">
+        <v>356</v>
+      </c>
+      <c r="AN17" t="s">
         <v>357</v>
       </c>
-      <c r="AN17" t="s">
-        <v>358</v>
-      </c>
       <c r="AO17">
-        <v>0.99802303154782224</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP17">
-        <v>36.244421623259619</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8328,13 +8328,13 @@
         <v>416</v>
       </c>
       <c r="BB17" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="BC17">
-        <v>0.99603343715055259</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD17">
-        <v>72.720318906536249</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8399,16 +8399,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.99834158364926728</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB18">
-        <v>30.404299763434018</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -8435,16 +8435,16 @@
         <v>319</v>
       </c>
       <c r="AM18" t="s">
+        <v>358</v>
+      </c>
+      <c r="AN18" t="s">
         <v>359</v>
       </c>
-      <c r="AN18" t="s">
-        <v>360</v>
-      </c>
       <c r="AO18">
-        <v>0.99714358927215652</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP18">
-        <v>52.367530010463909</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8471,16 +8471,16 @@
         <v>398</v>
       </c>
       <c r="BA18" t="s">
+        <v>417</v>
+      </c>
+      <c r="BB18" t="s">
         <v>418</v>
       </c>
-      <c r="BB18" t="s">
-        <v>419</v>
-      </c>
       <c r="BC18">
-        <v>0.99399718012600935</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD18">
-        <v>110.05169768982766</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8545,16 +8545,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.9987403722896917</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB19">
-        <v>23.093174688985375</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -8581,16 +8581,16 @@
         <v>321</v>
       </c>
       <c r="AM19" t="s">
+        <v>360</v>
+      </c>
+      <c r="AN19" t="s">
         <v>361</v>
       </c>
-      <c r="AN19" t="s">
-        <v>362</v>
-      </c>
       <c r="AO19">
-        <v>0.99873239758997023</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP19">
-        <v>23.239377517213022</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8617,16 +8617,16 @@
         <v>400</v>
       </c>
       <c r="BA19" t="s">
+        <v>419</v>
+      </c>
+      <c r="BB19" t="s">
         <v>420</v>
       </c>
-      <c r="BB19" t="s">
-        <v>421</v>
-      </c>
       <c r="BC19">
-        <v>0.99383395234396599</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD19">
-        <v>113.04420702728957</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8691,16 +8691,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99692898913090644</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB20">
-        <v>56.301865933381954</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8727,16 +8727,16 @@
         <v>323</v>
       </c>
       <c r="AM20" t="s">
+        <v>362</v>
+      </c>
+      <c r="AN20" t="s">
         <v>363</v>
       </c>
-      <c r="AN20" t="s">
-        <v>364</v>
-      </c>
       <c r="AO20">
-        <v>0.99635146162488653</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP20">
-        <v>66.889870210414614</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8763,16 +8763,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
+        <v>421</v>
+      </c>
+      <c r="BB20" t="s">
         <v>422</v>
       </c>
-      <c r="BB20" t="s">
-        <v>407</v>
-      </c>
       <c r="BC20">
-        <v>0.99564789206089888</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD20">
-        <v>79.788645550187297</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8837,16 +8837,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99763459325217896</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB21">
-        <v>43.365790376719588</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8873,16 +8873,16 @@
         <v>325</v>
       </c>
       <c r="AM21" t="s">
+        <v>364</v>
+      </c>
+      <c r="AN21" t="s">
         <v>365</v>
       </c>
-      <c r="AN21" t="s">
-        <v>303</v>
-      </c>
       <c r="AO21">
-        <v>0.99586212495478665</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP21">
-        <v>75.861042495577635</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8947,16 +8947,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99733507264559695</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB22">
-        <v>48.857001497390002</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -8989,10 +8989,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99653588726932718</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP22">
-        <v>63.508733395668145</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99583365539385327</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB23">
-        <v>76.382984446022675</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9099,10 +9099,10 @@
         <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99883902037019667</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP23">
-        <v>21.284626546395259</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9167,16 +9167,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99875154162789404</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB24">
-        <v>22.888403488609324</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9209,10 +9209,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99521984547821263</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP24">
-        <v>87.636166232768815</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9277,16 +9277,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99511607748745434</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB25">
-        <v>89.538579396670116</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -9319,10 +9319,10 @@
         <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.99749126227646956</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP25">
-        <v>45.993524931390482</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9387,16 +9387,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99801094175818605</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB26">
-        <v>36.466067766588218</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9429,10 +9429,10 @@
         <v>375</v>
       </c>
       <c r="AO26">
-        <v>0.99807543246352515</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP26">
-        <v>35.283738168705199</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9497,16 +9497,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99909366739195871</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB27">
-        <v>16.616097814091063</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9539,10 +9539,10 @@
         <v>377</v>
       </c>
       <c r="AO27">
-        <v>0.99826576737141715</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP27">
-        <v>31.794264857351436</v>
+        <v>28.402000808355538</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9607,16 +9607,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99648087644372252</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB28">
-        <v>64.517265198419722</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9649,10 +9649,10 @@
         <v>379</v>
       </c>
       <c r="AO28">
-        <v>0.99871360797890252</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP28">
-        <v>23.583853720120768</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9717,16 +9717,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99621535905375425</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB29">
-        <v>69.385084014505708</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -9759,10 +9759,10 @@
         <v>381</v>
       </c>
       <c r="AO29">
-        <v>0.99730422320290779</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP29">
-        <v>49.422574613357185</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9827,16 +9827,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="Z30" t="s">
         <v>304</v>
       </c>
       <c r="AA30">
-        <v>0.99505524223378883</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB30">
-        <v>90.653892380538664</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9869,10 +9869,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99805709209211746</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP30">
-        <v>35.619978311179104</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
   </sheetData>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99CF94F9-980A-4CC9-92C4-1C50D2769BEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A341FC6F-9831-4E25-8FBA-D3B97E982C2B}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9993,7 +9993,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10061,7 +10061,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10094,7 +10094,7 @@
         <v>465</v>
       </c>
       <c r="X12" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10129,7 +10129,7 @@
         <v>427</v>
       </c>
       <c r="K13" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10162,7 +10162,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10197,7 +10197,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10230,7 +10230,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10265,7 +10265,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10333,7 +10333,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10366,7 +10366,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10401,7 +10401,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10434,7 +10434,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10469,7 +10469,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10502,7 +10502,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10537,7 +10537,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10570,7 +10570,7 @@
         <v>479</v>
       </c>
       <c r="X19" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10605,7 +10605,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10638,7 +10638,7 @@
         <v>481</v>
       </c>
       <c r="X20" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10673,7 +10673,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10708,7 +10708,7 @@
         <v>445</v>
       </c>
       <c r="K22" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10743,7 +10743,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10778,7 +10778,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10813,7 +10813,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10848,7 +10848,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10883,7 +10883,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10918,7 +10918,7 @@
         <v>457</v>
       </c>
       <c r="K28" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10953,7 +10953,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -10988,7 +10988,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11003,7 +11003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F72E12E-1A85-4261-B68C-4C3BEFDBAF61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8CAF4E-3601-470F-948A-ED1C7767A6C9}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12820,7 +12820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2274994D-E095-49EF-8675-1E4F48780984}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD7E6AF-B303-453F-BAF7-B96D1BE95537}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13893,7 +13893,7 @@
         <v>569</v>
       </c>
       <c r="C36" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D36" t="s">
         <v>570</v>
@@ -13928,7 +13928,7 @@
         <v>570</v>
       </c>
       <c r="D37" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E37">
         <v>1</v>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{251F5FE6-DC91-47A5-8185-3BCFE282E421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C19075D2-D5AA-403E-B220-D240DFE932F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2811" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="767">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -856,18 +856,24 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -880,6 +886,42 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_015</t>
   </si>
   <si>
@@ -892,10 +934,34 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_010</t>
@@ -904,72 +970,6 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_014</t>
   </si>
   <si>
@@ -988,6 +988,9 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
     <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
   </si>
   <si>
@@ -997,175 +1000,283 @@
     <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
   </si>
   <si>
+    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+  </si>
+  <si>
     <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
   </si>
   <si>
     <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
   </si>
   <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
   </si>
   <si>
     <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
   </si>
   <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
     <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
   </si>
   <si>
     <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_017</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
@@ -1174,115 +1285,10 @@
     <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_005</t>
@@ -1297,42 +1303,36 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
@@ -1345,6 +1345,12 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL,e_w255314292_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
@@ -1357,39 +1363,33 @@
     <t>e_w112614319-400_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
     <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL,e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
@@ -1661,12 +1661,6 @@
   </si>
   <si>
     <t>en_biomass_ccs</t>
-  </si>
-  <si>
-    <t>en_hydro_large</t>
-  </si>
-  <si>
-    <t>en_hydro_small</t>
   </si>
   <si>
     <t>en_geothermal</t>
@@ -3493,7 +3487,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74BD0F4C-D3CD-6969-CEFA-FAE0A4B163FA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D63DC5A-A319-7E71-3FEC-9CC4A5AF789F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3548,7 +3542,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B727E181-8C54-FCC0-1938-4C5178316660}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C3C24B9-B9CA-E1F8-24E1-231B6D41C2C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3603,7 +3597,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17AFD512-790E-7E0D-24D7-6EA97D10D76F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC4DE43E-6015-4568-AC46-06C6D8191965}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3658,7 +3652,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ED98B70-451F-F75B-1A6A-F1BD7A9B3700}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1E8D7EF-D4A4-BCD3-B4D1-52B39E1C49E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4676,7 +4670,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -7477,7 +7471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769007F4-AF57-4184-BC99-324DDD4AC06D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5A328E-6408-48D2-A64E-E8A3A5D317C9}">
   <dimension ref="A1:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -7776,16 +7770,16 @@
         <v>242</v>
       </c>
       <c r="Y11" s="157" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="Z11" s="157" t="s">
         <v>286</v>
       </c>
       <c r="AA11" s="160">
-        <v>0.99733507264559695</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB11" s="163">
-        <v>48.857001497390002</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD11" s="157" t="s">
         <v>241</v>
@@ -7818,10 +7812,10 @@
         <v>347</v>
       </c>
       <c r="AO11" s="160">
-        <v>0.99776911581804295</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP11" s="163">
-        <v>40.899543335879912</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR11" s="157" t="s">
         <v>241</v>
@@ -7854,10 +7848,10 @@
         <v>406</v>
       </c>
       <c r="BC11" s="160">
-        <v>0.9932866968373224</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD11" s="163">
-        <v>123.07722464908932</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="12" spans="1:56">
@@ -7922,16 +7916,16 @@
         <v>246</v>
       </c>
       <c r="Y12" s="158" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z12" s="158" t="s">
         <v>287</v>
       </c>
       <c r="AA12" s="162">
-        <v>0.99583365539385327</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB12" s="164">
-        <v>76.382984446022675</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD12" s="158" t="s">
         <v>241</v>
@@ -7964,10 +7958,10 @@
         <v>349</v>
       </c>
       <c r="AO12" s="162">
-        <v>0.99641308487583879</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP12" s="164">
-        <v>65.760110609622657</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR12" s="158" t="s">
         <v>241</v>
@@ -8000,10 +7994,10 @@
         <v>408</v>
       </c>
       <c r="BC12" s="162">
-        <v>0.99644388872049838</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD12" s="164">
-        <v>65.195373457529499</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="13" spans="1:56">
@@ -8068,16 +8062,16 @@
         <v>248</v>
       </c>
       <c r="Y13" s="157" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="Z13" s="157" t="s">
         <v>288</v>
       </c>
       <c r="AA13" s="160">
-        <v>0.99875154162789404</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB13" s="163">
-        <v>22.888403488609324</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD13" s="157" t="s">
         <v>241</v>
@@ -8110,10 +8104,10 @@
         <v>351</v>
       </c>
       <c r="AO13" s="160">
-        <v>0.99449756685866841</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP13" s="163">
-        <v>100.87794092441324</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR13" s="157" t="s">
         <v>241</v>
@@ -8146,10 +8140,10 @@
         <v>410</v>
       </c>
       <c r="BC13" s="160">
-        <v>0.99603343715055259</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD13" s="163">
-        <v>72.720318906536249</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="14" spans="1:56">
@@ -8214,16 +8208,16 @@
         <v>250</v>
       </c>
       <c r="Y14" s="158" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Z14" s="158" t="s">
         <v>289</v>
       </c>
       <c r="AA14" s="162">
-        <v>0.99860106452186825</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB14" s="164">
-        <v>25.647150432415483</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD14" s="158" t="s">
         <v>241</v>
@@ -8256,10 +8250,10 @@
         <v>353</v>
       </c>
       <c r="AO14" s="162">
-        <v>0.99730422320290779</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP14" s="164">
-        <v>49.422574613357185</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR14" s="158" t="s">
         <v>241</v>
@@ -8360,16 +8354,16 @@
         <v>252</v>
       </c>
       <c r="Y15" s="157" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="Z15" s="157" t="s">
         <v>290</v>
       </c>
       <c r="AA15" s="160">
-        <v>0.99775856069920277</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB15" s="163">
-        <v>41.093053847949164</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD15" s="157" t="s">
         <v>241</v>
@@ -8402,10 +8396,10 @@
         <v>355</v>
       </c>
       <c r="AO15" s="160">
-        <v>0.99805709209211746</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP15" s="163">
-        <v>35.619978311179104</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR15" s="157" t="s">
         <v>241</v>
@@ -8506,16 +8500,16 @@
         <v>254</v>
       </c>
       <c r="Y16" s="158" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="Z16" s="158" t="s">
         <v>291</v>
       </c>
       <c r="AA16" s="162">
-        <v>0.99572127940552169</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB16" s="164">
-        <v>78.443210898768598</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD16" s="158" t="s">
         <v>241</v>
@@ -8548,10 +8542,10 @@
         <v>357</v>
       </c>
       <c r="AO16" s="162">
-        <v>0.99845079995590791</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP16" s="164">
-        <v>28.402000808355538</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR16" s="158" t="s">
         <v>241</v>
@@ -8584,10 +8578,10 @@
         <v>416</v>
       </c>
       <c r="BC16" s="162">
-        <v>0.99399718012600935</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD16" s="164">
-        <v>110.05169768982766</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8652,16 +8646,16 @@
         <v>256</v>
       </c>
       <c r="Y17" s="157" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="Z17" s="157" t="s">
         <v>292</v>
       </c>
       <c r="AA17" s="160">
-        <v>0.99511607748745434</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB17" s="163">
-        <v>89.538579396670116</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD17" s="157" t="s">
         <v>241</v>
@@ -8691,13 +8685,13 @@
         <v>358</v>
       </c>
       <c r="AN17" s="157" t="s">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="AO17" s="160">
-        <v>0.9963019969989696</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP17" s="163">
-        <v>67.796721685557472</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR17" s="157" t="s">
         <v>241</v>
@@ -8727,13 +8721,13 @@
         <v>417</v>
       </c>
       <c r="BB17" s="157" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="BC17" s="160">
-        <v>0.99383395234396599</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD17" s="163">
-        <v>113.04420702728957</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8798,16 +8792,16 @@
         <v>258</v>
       </c>
       <c r="Y18" s="158" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Z18" s="158" t="s">
         <v>293</v>
       </c>
       <c r="AA18" s="162">
-        <v>0.99729953359766199</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB18" s="164">
-        <v>49.508550709529651</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD18" s="158" t="s">
         <v>241</v>
@@ -8834,16 +8828,16 @@
         <v>320</v>
       </c>
       <c r="AM18" s="158" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN18" s="158" t="s">
         <v>360</v>
       </c>
-      <c r="AN18" s="158" t="s">
-        <v>361</v>
-      </c>
       <c r="AO18" s="162">
-        <v>0.99873239758997023</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP18" s="164">
-        <v>23.239377517213022</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR18" s="158" t="s">
         <v>241</v>
@@ -8870,16 +8864,16 @@
         <v>399</v>
       </c>
       <c r="BA18" s="158" t="s">
+        <v>418</v>
+      </c>
+      <c r="BB18" s="158" t="s">
         <v>419</v>
       </c>
-      <c r="BB18" s="158" t="s">
-        <v>408</v>
-      </c>
       <c r="BC18" s="162">
-        <v>0.99564789206089888</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD18" s="164">
-        <v>79.788645550187297</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8980,16 +8974,16 @@
         <v>322</v>
       </c>
       <c r="AM19" s="157" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN19" s="157" t="s">
         <v>362</v>
       </c>
-      <c r="AN19" s="157" t="s">
-        <v>363</v>
-      </c>
       <c r="AO19" s="160">
-        <v>0.99826576737141715</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP19" s="163">
-        <v>31.794264857351436</v>
+        <v>28.402000808355538</v>
       </c>
       <c r="AR19" s="157" t="s">
         <v>241</v>
@@ -9090,16 +9084,16 @@
         <v>262</v>
       </c>
       <c r="Y20" s="158" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Z20" s="158" t="s">
         <v>295</v>
       </c>
       <c r="AA20" s="162">
-        <v>0.99738245649758195</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB20" s="164">
-        <v>47.988297544331637</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD20" s="158" t="s">
         <v>241</v>
@@ -9126,16 +9120,16 @@
         <v>324</v>
       </c>
       <c r="AM20" s="158" t="s">
+        <v>363</v>
+      </c>
+      <c r="AN20" s="158" t="s">
         <v>364</v>
       </c>
-      <c r="AN20" s="158" t="s">
-        <v>365</v>
-      </c>
       <c r="AO20" s="162">
-        <v>0.99871360797890252</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP20" s="164">
-        <v>23.583853720120768</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR20" s="158" t="s">
         <v>241</v>
@@ -9236,16 +9230,16 @@
         <v>264</v>
       </c>
       <c r="Y21" s="157" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Z21" s="157" t="s">
         <v>296</v>
       </c>
       <c r="AA21" s="160">
-        <v>0.99692898913090644</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB21" s="163">
-        <v>56.301865933381954</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD21" s="157" t="s">
         <v>241</v>
@@ -9272,16 +9266,16 @@
         <v>326</v>
       </c>
       <c r="AM21" s="157" t="s">
+        <v>365</v>
+      </c>
+      <c r="AN21" s="157" t="s">
         <v>366</v>
       </c>
-      <c r="AN21" s="157" t="s">
-        <v>367</v>
-      </c>
       <c r="AO21" s="160">
-        <v>0.99653588726932718</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP21" s="163">
-        <v>63.508733395668145</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9346,16 +9340,16 @@
         <v>266</v>
       </c>
       <c r="Y22" s="158" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="Z22" s="158" t="s">
         <v>297</v>
       </c>
       <c r="AA22" s="162">
-        <v>0.99505524223378883</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB22" s="164">
-        <v>90.653892380538664</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD22" s="158" t="s">
         <v>241</v>
@@ -9382,16 +9376,16 @@
         <v>328</v>
       </c>
       <c r="AM22" s="158" t="s">
+        <v>367</v>
+      </c>
+      <c r="AN22" s="158" t="s">
         <v>368</v>
       </c>
-      <c r="AN22" s="158" t="s">
-        <v>369</v>
-      </c>
       <c r="AO22" s="162">
-        <v>0.99635146162488653</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP22" s="164">
-        <v>66.889870210414614</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9456,16 +9450,16 @@
         <v>268</v>
       </c>
       <c r="Y23" s="157" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z23" s="157" t="s">
         <v>298</v>
       </c>
       <c r="AA23" s="160">
-        <v>0.99763459325217896</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB23" s="163">
-        <v>43.365790376719588</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD23" s="157" t="s">
         <v>241</v>
@@ -9492,16 +9486,16 @@
         <v>330</v>
       </c>
       <c r="AM23" s="157" t="s">
+        <v>369</v>
+      </c>
+      <c r="AN23" s="157" t="s">
         <v>370</v>
       </c>
-      <c r="AN23" s="157" t="s">
-        <v>300</v>
-      </c>
       <c r="AO23" s="160">
-        <v>0.99586212495478665</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP23" s="163">
-        <v>75.861042495577635</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9566,16 +9560,16 @@
         <v>270</v>
       </c>
       <c r="Y24" s="158" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="Z24" s="158" t="s">
         <v>299</v>
       </c>
       <c r="AA24" s="162">
-        <v>0.99648087644372252</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB24" s="164">
-        <v>64.517265198419722</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD24" s="158" t="s">
         <v>241</v>
@@ -9608,10 +9602,10 @@
         <v>372</v>
       </c>
       <c r="AO24" s="162">
-        <v>0.99883902037019667</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP24" s="164">
-        <v>21.284626546395259</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9676,16 +9670,16 @@
         <v>272</v>
       </c>
       <c r="Y25" s="157" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Z25" s="157" t="s">
         <v>300</v>
       </c>
       <c r="AA25" s="160">
-        <v>0.99621535905375425</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB25" s="163">
-        <v>69.385084014505708</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD25" s="157" t="s">
         <v>241</v>
@@ -9718,10 +9712,10 @@
         <v>374</v>
       </c>
       <c r="AO25" s="160">
-        <v>0.99521984547821263</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP25" s="163">
-        <v>87.636166232768815</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9786,16 +9780,16 @@
         <v>274</v>
       </c>
       <c r="Y26" s="158" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z26" s="158" t="s">
         <v>301</v>
       </c>
       <c r="AA26" s="162">
-        <v>0.99812712894455979</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB26" s="164">
-        <v>34.335969349736395</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD26" s="158" t="s">
         <v>241</v>
@@ -9828,10 +9822,10 @@
         <v>376</v>
       </c>
       <c r="AO26" s="162">
-        <v>0.99622969699231045</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP26" s="164">
-        <v>69.122221807641537</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9896,16 +9890,16 @@
         <v>276</v>
       </c>
       <c r="Y27" s="157" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Z27" s="157" t="s">
         <v>302</v>
       </c>
       <c r="AA27" s="160">
-        <v>0.99834158364926728</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB27" s="163">
-        <v>30.404299763434018</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD27" s="157" t="s">
         <v>241</v>
@@ -9938,10 +9932,10 @@
         <v>378</v>
       </c>
       <c r="AO27" s="160">
-        <v>0.99749126227646956</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP27" s="163">
-        <v>45.993524931390482</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10006,16 +10000,16 @@
         <v>278</v>
       </c>
       <c r="Y28" s="158" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Z28" s="158" t="s">
         <v>303</v>
       </c>
       <c r="AA28" s="162">
-        <v>0.9987403722896917</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB28" s="164">
-        <v>23.093174688985375</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD28" s="158" t="s">
         <v>241</v>
@@ -10048,10 +10042,10 @@
         <v>380</v>
       </c>
       <c r="AO28" s="162">
-        <v>0.99807543246352515</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP28" s="164">
-        <v>35.283738168705199</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10158,10 +10152,10 @@
         <v>382</v>
       </c>
       <c r="AO29" s="160">
-        <v>0.99802303154782224</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP29" s="163">
-        <v>36.244421623259619</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10268,10 +10262,10 @@
         <v>384</v>
       </c>
       <c r="AO30" s="162">
-        <v>0.99714358927215652</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP30" s="164">
-        <v>52.367530010463909</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
   </sheetData>
@@ -10284,7 +10278,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8AB741-D60F-4685-9F8D-2D594CB3F990}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0010094-1E9C-4FCA-ADAC-508BBCAA9670}">
   <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -10430,7 +10424,7 @@
         <v>424</v>
       </c>
       <c r="K11" s="157" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L11" s="159">
         <v>0.30278350605008381</v>
@@ -10463,7 +10457,7 @@
         <v>464</v>
       </c>
       <c r="X11" s="157" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y11" s="159">
         <v>0.83925000000000005</v>
@@ -10498,7 +10492,7 @@
         <v>426</v>
       </c>
       <c r="K12" s="158" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="L12" s="161">
         <v>0.44035497786033617</v>
@@ -10566,7 +10560,7 @@
         <v>428</v>
       </c>
       <c r="K13" s="157" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L13" s="159">
         <v>1.6077871713950227</v>
@@ -10599,7 +10593,7 @@
         <v>468</v>
       </c>
       <c r="X13" s="157" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y13" s="159">
         <v>11.2965</v>
@@ -10634,7 +10628,7 @@
         <v>430</v>
       </c>
       <c r="K14" s="158" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="L14" s="161">
         <v>2.531891424764753</v>
@@ -10702,7 +10696,7 @@
         <v>432</v>
       </c>
       <c r="K15" s="157" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L15" s="159">
         <v>7.6497810049421515</v>
@@ -10735,7 +10729,7 @@
         <v>472</v>
       </c>
       <c r="X15" s="157" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Y15" s="159">
         <v>17.089500000000001</v>
@@ -10770,7 +10764,7 @@
         <v>434</v>
       </c>
       <c r="K16" s="158" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L16" s="161">
         <v>0.63333325583919986</v>
@@ -10838,7 +10832,7 @@
         <v>436</v>
       </c>
       <c r="K17" s="157" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="L17" s="159">
         <v>0.78389041837100704</v>
@@ -10871,7 +10865,7 @@
         <v>476</v>
       </c>
       <c r="X17" s="157" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="Y17" s="159">
         <v>0.22650000000000001</v>
@@ -10906,7 +10900,7 @@
         <v>438</v>
       </c>
       <c r="K18" s="158" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="L18" s="161">
         <v>3.0365724666245324</v>
@@ -10939,7 +10933,7 @@
         <v>478</v>
       </c>
       <c r="X18" s="158" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Y18" s="161">
         <v>9.5062499999999996</v>
@@ -10974,7 +10968,7 @@
         <v>440</v>
       </c>
       <c r="K19" s="157" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="L19" s="159">
         <v>0.22970161230087291</v>
@@ -11007,7 +11001,7 @@
         <v>480</v>
       </c>
       <c r="X19" s="157" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="Y19" s="159">
         <v>13.37175</v>
@@ -11042,7 +11036,7 @@
         <v>442</v>
       </c>
       <c r="K20" s="158" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="L20" s="161">
         <v>0.27066515065379043</v>
@@ -11110,7 +11104,7 @@
         <v>444</v>
       </c>
       <c r="K21" s="157" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="L21" s="159">
         <v>0.32193208719379746</v>
@@ -11145,7 +11139,7 @@
         <v>446</v>
       </c>
       <c r="K22" s="158" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L22" s="161">
         <v>0.6573344927201471</v>
@@ -11180,7 +11174,7 @@
         <v>448</v>
       </c>
       <c r="K23" s="157" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="L23" s="159">
         <v>0.28992997651770519</v>
@@ -11215,7 +11209,7 @@
         <v>450</v>
       </c>
       <c r="K24" s="158" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="L24" s="161">
         <v>0.74609319967150689</v>
@@ -11250,7 +11244,7 @@
         <v>452</v>
       </c>
       <c r="K25" s="157" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L25" s="159">
         <v>0.35328950844501877</v>
@@ -11285,7 +11279,7 @@
         <v>454</v>
       </c>
       <c r="K26" s="158" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L26" s="161">
         <v>0.7924639655878376</v>
@@ -11320,7 +11314,7 @@
         <v>456</v>
       </c>
       <c r="K27" s="157" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="L27" s="159">
         <v>0.55411362221124194</v>
@@ -11355,7 +11349,7 @@
         <v>458</v>
       </c>
       <c r="K28" s="158" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L28" s="161">
         <v>1.4327274230737423</v>
@@ -11390,7 +11384,7 @@
         <v>460</v>
       </c>
       <c r="K29" s="157" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="L29" s="159">
         <v>0.58742801517356968</v>
@@ -11425,7 +11419,7 @@
         <v>462</v>
       </c>
       <c r="K30" s="158" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L30" s="161">
         <v>0.35405891742987328</v>
@@ -11444,8 +11438,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E6B358-F6F5-475B-9096-4E15730F9E5E}">
-  <dimension ref="A1:S142"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D35205A-D1C6-4400-899E-CE128140058A}">
+  <dimension ref="A1:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="18.53125" bestFit="1" customWidth="1"/>
@@ -11574,7 +11568,7 @@
         <v>245</v>
       </c>
       <c r="S11" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -11619,7 +11613,7 @@
         <v>245</v>
       </c>
       <c r="S12" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -11648,7 +11642,7 @@
         <v>487</v>
       </c>
       <c r="M13" s="157" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N13" s="157" t="s">
         <v>491</v>
@@ -11664,7 +11658,7 @@
         <v>245</v>
       </c>
       <c r="S13" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -11709,7 +11703,7 @@
         <v>245</v>
       </c>
       <c r="S14" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -11760,7 +11754,7 @@
         <v>245</v>
       </c>
       <c r="S15" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -11811,7 +11805,7 @@
         <v>245</v>
       </c>
       <c r="S16" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="2:19">
@@ -11856,7 +11850,7 @@
         <v>245</v>
       </c>
       <c r="S17" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="2:19">
@@ -11901,7 +11895,7 @@
         <v>245</v>
       </c>
       <c r="S18" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -11946,7 +11940,7 @@
         <v>245</v>
       </c>
       <c r="S19" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="2:19">
@@ -11991,7 +11985,7 @@
         <v>245</v>
       </c>
       <c r="S20" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="2:19">
@@ -12042,7 +12036,7 @@
         <v>245</v>
       </c>
       <c r="S21" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="22" spans="2:19">
@@ -12093,7 +12087,7 @@
         <v>245</v>
       </c>
       <c r="S22" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" spans="2:19">
@@ -12138,7 +12132,7 @@
         <v>245</v>
       </c>
       <c r="S23" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" spans="2:19">
@@ -12183,7 +12177,7 @@
         <v>245</v>
       </c>
       <c r="S24" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="25" spans="2:19">
@@ -12228,7 +12222,7 @@
         <v>245</v>
       </c>
       <c r="S25" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" spans="2:19">
@@ -12273,7 +12267,7 @@
         <v>245</v>
       </c>
       <c r="S26" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="27" spans="2:19">
@@ -12308,7 +12302,7 @@
         <v>488</v>
       </c>
       <c r="M27" s="157" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N27" s="157" t="s">
         <v>509</v>
@@ -12324,7 +12318,7 @@
         <v>245</v>
       </c>
       <c r="S27" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="2:19">
@@ -12375,7 +12369,7 @@
         <v>245</v>
       </c>
       <c r="S28" s="158" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="29" spans="2:19">
@@ -12426,7 +12420,7 @@
         <v>245</v>
       </c>
       <c r="S29" s="157" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="2:19">
@@ -12454,25 +12448,6 @@
       <c r="K30" s="158" t="s">
         <v>485</v>
       </c>
-      <c r="M30" s="158" t="s">
-        <v>172</v>
-      </c>
-      <c r="N30" s="158" t="s">
-        <v>512</v>
-      </c>
-      <c r="O30" s="158"/>
-      <c r="P30" s="158" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q30" s="158" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" s="158" t="s">
-        <v>245</v>
-      </c>
-      <c r="S30" s="158" t="s">
-        <v>514</v>
-      </c>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="157" t="s">
@@ -12499,25 +12474,6 @@
       <c r="K31" s="157" t="s">
         <v>486</v>
       </c>
-      <c r="M31" s="157" t="s">
-        <v>172</v>
-      </c>
-      <c r="N31" s="157" t="s">
-        <v>513</v>
-      </c>
-      <c r="O31" s="157"/>
-      <c r="P31" s="157" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q31" s="157" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" s="157" t="s">
-        <v>245</v>
-      </c>
-      <c r="S31" s="157" t="s">
-        <v>514</v>
-      </c>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="158" t="s">
@@ -15060,22 +15016,22 @@
         <v>511</v>
       </c>
       <c r="C122" s="158" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D122" s="158" t="s">
         <v>19</v>
       </c>
       <c r="E122" s="164">
-        <v>2650</v>
+        <v>2850</v>
       </c>
       <c r="F122" s="164">
-        <v>2650</v>
+        <v>2750</v>
       </c>
       <c r="G122" s="164"/>
       <c r="H122" s="164"/>
       <c r="I122" s="164"/>
       <c r="J122" s="164">
-        <v>2650</v>
+        <v>2550</v>
       </c>
       <c r="K122" s="158" t="s">
         <v>485</v>
@@ -15086,22 +15042,22 @@
         <v>511</v>
       </c>
       <c r="C123" s="157" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D123" s="157" t="s">
         <v>19</v>
       </c>
       <c r="E123" s="163">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F123" s="163">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G123" s="163"/>
       <c r="H123" s="163"/>
       <c r="I123" s="163"/>
       <c r="J123" s="163">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K123" s="157" t="s">
         <v>486</v>
@@ -15112,7 +15068,7 @@
         <v>511</v>
       </c>
       <c r="C124" s="158" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D124" s="158" t="s">
         <v>19</v>
@@ -15138,22 +15094,22 @@
         <v>511</v>
       </c>
       <c r="C125" s="157" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D125" s="157" t="s">
         <v>19</v>
       </c>
       <c r="E125" s="163">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F125" s="163">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G125" s="163"/>
       <c r="H125" s="163"/>
       <c r="I125" s="163"/>
       <c r="J125" s="163">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K125" s="157" t="s">
         <v>146</v>
@@ -15164,22 +15120,22 @@
         <v>511</v>
       </c>
       <c r="C126" s="158" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D126" s="158" t="s">
         <v>19</v>
       </c>
       <c r="E126" s="164">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="F126" s="164">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="G126" s="164"/>
       <c r="H126" s="164"/>
       <c r="I126" s="164"/>
       <c r="J126" s="164">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="K126" s="158" t="s">
         <v>507</v>
@@ -15190,28 +15146,28 @@
         <v>511</v>
       </c>
       <c r="C127" s="157" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D127" s="157" t="s">
         <v>19</v>
       </c>
       <c r="E127" s="163">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F127" s="163">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G127" s="163">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H127" s="163">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I127" s="163">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J127" s="163">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K127" s="157" t="s">
         <v>488</v>
@@ -15222,7 +15178,7 @@
         <v>511</v>
       </c>
       <c r="C128" s="158" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D128" s="158" t="s">
         <v>19</v>
@@ -15246,394 +15202,6 @@
         <v>4</v>
       </c>
       <c r="K128" s="158" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="129" spans="2:11">
-      <c r="B129" s="157" t="s">
-        <v>512</v>
-      </c>
-      <c r="C129" s="157" t="s">
-        <v>28</v>
-      </c>
-      <c r="D129" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="163">
-        <v>3900</v>
-      </c>
-      <c r="F129" s="163">
-        <v>3900</v>
-      </c>
-      <c r="G129" s="163"/>
-      <c r="H129" s="163"/>
-      <c r="I129" s="163"/>
-      <c r="J129" s="163">
-        <v>3900</v>
-      </c>
-      <c r="K129" s="157" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="130" spans="2:11">
-      <c r="B130" s="158" t="s">
-        <v>512</v>
-      </c>
-      <c r="C130" s="158" t="s">
-        <v>28</v>
-      </c>
-      <c r="D130" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="164">
-        <v>80</v>
-      </c>
-      <c r="F130" s="164">
-        <v>80</v>
-      </c>
-      <c r="G130" s="164"/>
-      <c r="H130" s="164"/>
-      <c r="I130" s="164"/>
-      <c r="J130" s="164">
-        <v>80</v>
-      </c>
-      <c r="K130" s="158" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="131" spans="2:11">
-      <c r="B131" s="157" t="s">
-        <v>512</v>
-      </c>
-      <c r="C131" s="157" t="s">
-        <v>28</v>
-      </c>
-      <c r="D131" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" s="163">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="F131" s="163">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="G131" s="163"/>
-      <c r="H131" s="163"/>
-      <c r="I131" s="163"/>
-      <c r="J131" s="163">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="K131" s="157" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="132" spans="2:11">
-      <c r="B132" s="158" t="s">
-        <v>512</v>
-      </c>
-      <c r="C132" s="158" t="s">
-        <v>28</v>
-      </c>
-      <c r="D132" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="164">
-        <v>1</v>
-      </c>
-      <c r="F132" s="164">
-        <v>1</v>
-      </c>
-      <c r="G132" s="164"/>
-      <c r="H132" s="164"/>
-      <c r="I132" s="164"/>
-      <c r="J132" s="164">
-        <v>1</v>
-      </c>
-      <c r="K132" s="158" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="133" spans="2:11">
-      <c r="B133" s="157" t="s">
-        <v>512</v>
-      </c>
-      <c r="C133" s="157" t="s">
-        <v>28</v>
-      </c>
-      <c r="D133" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="163">
-        <v>0.25</v>
-      </c>
-      <c r="F133" s="163">
-        <v>0.25</v>
-      </c>
-      <c r="G133" s="163"/>
-      <c r="H133" s="163"/>
-      <c r="I133" s="163"/>
-      <c r="J133" s="163">
-        <v>0.25</v>
-      </c>
-      <c r="K133" s="157" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="134" spans="2:11">
-      <c r="B134" s="158" t="s">
-        <v>512</v>
-      </c>
-      <c r="C134" s="158" t="s">
-        <v>28</v>
-      </c>
-      <c r="D134" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="164">
-        <v>60</v>
-      </c>
-      <c r="F134" s="164">
-        <v>60</v>
-      </c>
-      <c r="G134" s="164">
-        <v>60</v>
-      </c>
-      <c r="H134" s="164">
-        <v>60</v>
-      </c>
-      <c r="I134" s="164">
-        <v>60</v>
-      </c>
-      <c r="J134" s="164">
-        <v>60</v>
-      </c>
-      <c r="K134" s="158" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="135" spans="2:11">
-      <c r="B135" s="157" t="s">
-        <v>512</v>
-      </c>
-      <c r="C135" s="157" t="s">
-        <v>28</v>
-      </c>
-      <c r="D135" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E135" s="163">
-        <v>4</v>
-      </c>
-      <c r="F135" s="163">
-        <v>4</v>
-      </c>
-      <c r="G135" s="163">
-        <v>4</v>
-      </c>
-      <c r="H135" s="163">
-        <v>4</v>
-      </c>
-      <c r="I135" s="163">
-        <v>4</v>
-      </c>
-      <c r="J135" s="163">
-        <v>4</v>
-      </c>
-      <c r="K135" s="157" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="136" spans="2:11">
-      <c r="B136" s="158" t="s">
-        <v>513</v>
-      </c>
-      <c r="C136" s="158" t="s">
-        <v>34</v>
-      </c>
-      <c r="D136" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E136" s="164">
-        <v>2850</v>
-      </c>
-      <c r="F136" s="164">
-        <v>2750</v>
-      </c>
-      <c r="G136" s="164"/>
-      <c r="H136" s="164"/>
-      <c r="I136" s="164"/>
-      <c r="J136" s="164">
-        <v>2550</v>
-      </c>
-      <c r="K136" s="158" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="137" spans="2:11">
-      <c r="B137" s="157" t="s">
-        <v>513</v>
-      </c>
-      <c r="C137" s="157" t="s">
-        <v>34</v>
-      </c>
-      <c r="D137" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="163">
-        <v>55</v>
-      </c>
-      <c r="F137" s="163">
-        <v>55</v>
-      </c>
-      <c r="G137" s="163"/>
-      <c r="H137" s="163"/>
-      <c r="I137" s="163"/>
-      <c r="J137" s="163">
-        <v>50</v>
-      </c>
-      <c r="K137" s="157" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="138" spans="2:11">
-      <c r="B138" s="158" t="s">
-        <v>513</v>
-      </c>
-      <c r="C138" s="158" t="s">
-        <v>34</v>
-      </c>
-      <c r="D138" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E138" s="164">
-        <v>0</v>
-      </c>
-      <c r="F138" s="164">
-        <v>0</v>
-      </c>
-      <c r="G138" s="164"/>
-      <c r="H138" s="164"/>
-      <c r="I138" s="164"/>
-      <c r="J138" s="164">
-        <v>0</v>
-      </c>
-      <c r="K138" s="158" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="139" spans="2:11">
-      <c r="B139" s="157" t="s">
-        <v>513</v>
-      </c>
-      <c r="C139" s="157" t="s">
-        <v>34</v>
-      </c>
-      <c r="D139" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E139" s="163">
-        <v>0.1</v>
-      </c>
-      <c r="F139" s="163">
-        <v>0.1</v>
-      </c>
-      <c r="G139" s="163"/>
-      <c r="H139" s="163"/>
-      <c r="I139" s="163"/>
-      <c r="J139" s="163">
-        <v>0.1</v>
-      </c>
-      <c r="K139" s="157" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="140" spans="2:11">
-      <c r="B140" s="158" t="s">
-        <v>513</v>
-      </c>
-      <c r="C140" s="158" t="s">
-        <v>34</v>
-      </c>
-      <c r="D140" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E140" s="164">
-        <v>0.85</v>
-      </c>
-      <c r="F140" s="164">
-        <v>0.85</v>
-      </c>
-      <c r="G140" s="164"/>
-      <c r="H140" s="164"/>
-      <c r="I140" s="164"/>
-      <c r="J140" s="164">
-        <v>0.85</v>
-      </c>
-      <c r="K140" s="158" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="141" spans="2:11">
-      <c r="B141" s="157" t="s">
-        <v>513</v>
-      </c>
-      <c r="C141" s="157" t="s">
-        <v>34</v>
-      </c>
-      <c r="D141" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E141" s="163">
-        <v>30</v>
-      </c>
-      <c r="F141" s="163">
-        <v>30</v>
-      </c>
-      <c r="G141" s="163">
-        <v>30</v>
-      </c>
-      <c r="H141" s="163">
-        <v>30</v>
-      </c>
-      <c r="I141" s="163">
-        <v>30</v>
-      </c>
-      <c r="J141" s="163">
-        <v>30</v>
-      </c>
-      <c r="K141" s="157" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="142" spans="2:11">
-      <c r="B142" s="158" t="s">
-        <v>513</v>
-      </c>
-      <c r="C142" s="158" t="s">
-        <v>34</v>
-      </c>
-      <c r="D142" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E142" s="164">
-        <v>4</v>
-      </c>
-      <c r="F142" s="164">
-        <v>4</v>
-      </c>
-      <c r="G142" s="164">
-        <v>4</v>
-      </c>
-      <c r="H142" s="164">
-        <v>4</v>
-      </c>
-      <c r="I142" s="164">
-        <v>4</v>
-      </c>
-      <c r="J142" s="164">
-        <v>4</v>
-      </c>
-      <c r="K142" s="158" t="s">
         <v>489</v>
       </c>
     </row>
@@ -15647,7 +15215,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4496682-ED31-4825-BA17-51F3B06C915B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9771A809-130B-46F3-9CE3-EA320FC98338}">
   <dimension ref="A1:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -15705,10 +15273,10 @@
         <v>167</v>
       </c>
       <c r="K3" s="156" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L3" s="156" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M3" s="156" t="s">
         <v>170</v>
@@ -15716,13 +15284,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="B4" s="157" t="s">
+        <v>514</v>
+      </c>
+      <c r="C4" s="157" t="s">
+        <v>515</v>
+      </c>
+      <c r="D4" s="157" t="s">
         <v>516</v>
-      </c>
-      <c r="C4" s="157" t="s">
-        <v>517</v>
-      </c>
-      <c r="D4" s="157" t="s">
-        <v>518</v>
       </c>
       <c r="E4" s="159">
         <v>1</v>
@@ -15731,10 +15299,10 @@
         <v>241</v>
       </c>
       <c r="I4" s="157" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="J4" s="157" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K4" s="157" t="s">
         <v>21</v>
@@ -15748,13 +15316,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="B5" s="158" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C5" s="158" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D5" s="158" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E5" s="161">
         <v>1</v>
@@ -15763,10 +15331,10 @@
         <v>241</v>
       </c>
       <c r="I5" s="158" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="J5" s="158" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="K5" s="158" t="s">
         <v>21</v>
@@ -15780,13 +15348,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="157" t="s">
+        <v>518</v>
+      </c>
+      <c r="C6" s="157" t="s">
+        <v>519</v>
+      </c>
+      <c r="D6" s="157" t="s">
         <v>520</v>
-      </c>
-      <c r="C6" s="157" t="s">
-        <v>521</v>
-      </c>
-      <c r="D6" s="157" t="s">
-        <v>522</v>
       </c>
       <c r="E6" s="159">
         <v>1</v>
@@ -15795,10 +15363,10 @@
         <v>241</v>
       </c>
       <c r="I6" s="157" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J6" s="157" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K6" s="157" t="s">
         <v>21</v>
@@ -15812,13 +15380,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="B7" s="158" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C7" s="158" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D7" s="158" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E7" s="161">
         <v>1</v>
@@ -15827,10 +15395,10 @@
         <v>241</v>
       </c>
       <c r="I7" s="158" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J7" s="158" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K7" s="158" t="s">
         <v>21</v>
@@ -15844,13 +15412,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="B8" s="157" t="s">
+        <v>522</v>
+      </c>
+      <c r="C8" s="157" t="s">
+        <v>523</v>
+      </c>
+      <c r="D8" s="157" t="s">
         <v>524</v>
-      </c>
-      <c r="C8" s="157" t="s">
-        <v>525</v>
-      </c>
-      <c r="D8" s="157" t="s">
-        <v>526</v>
       </c>
       <c r="E8" s="159">
         <v>1</v>
@@ -15859,10 +15427,10 @@
         <v>241</v>
       </c>
       <c r="I8" s="157" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J8" s="157" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="K8" s="157" t="s">
         <v>21</v>
@@ -15876,13 +15444,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="B9" s="158" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C9" s="158" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D9" s="158" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E9" s="161">
         <v>1</v>
@@ -15891,10 +15459,10 @@
         <v>241</v>
       </c>
       <c r="I9" s="158" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J9" s="158" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="K9" s="158" t="s">
         <v>21</v>
@@ -15908,13 +15476,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="B10" s="157" t="s">
+        <v>526</v>
+      </c>
+      <c r="C10" s="157" t="s">
+        <v>527</v>
+      </c>
+      <c r="D10" s="157" t="s">
         <v>528</v>
-      </c>
-      <c r="C10" s="157" t="s">
-        <v>529</v>
-      </c>
-      <c r="D10" s="157" t="s">
-        <v>530</v>
       </c>
       <c r="E10" s="159">
         <v>1</v>
@@ -15923,10 +15491,10 @@
         <v>241</v>
       </c>
       <c r="I10" s="157" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J10" s="157" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K10" s="157" t="s">
         <v>21</v>
@@ -15940,13 +15508,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="B11" s="158" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C11" s="158" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D11" s="158" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E11" s="161">
         <v>1</v>
@@ -15955,10 +15523,10 @@
         <v>241</v>
       </c>
       <c r="I11" s="158" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="J11" s="158" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K11" s="158" t="s">
         <v>21</v>
@@ -15972,13 +15540,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="B12" s="157" t="s">
+        <v>530</v>
+      </c>
+      <c r="C12" s="157" t="s">
+        <v>531</v>
+      </c>
+      <c r="D12" s="157" t="s">
         <v>532</v>
-      </c>
-      <c r="C12" s="157" t="s">
-        <v>533</v>
-      </c>
-      <c r="D12" s="157" t="s">
-        <v>534</v>
       </c>
       <c r="E12" s="159">
         <v>1</v>
@@ -15987,10 +15555,10 @@
         <v>241</v>
       </c>
       <c r="I12" s="157" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J12" s="157" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K12" s="157" t="s">
         <v>21</v>
@@ -16004,13 +15572,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="B13" s="158" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C13" s="158" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D13" s="158" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E13" s="161">
         <v>1</v>
@@ -16019,10 +15587,10 @@
         <v>241</v>
       </c>
       <c r="I13" s="158" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="J13" s="158" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K13" s="158" t="s">
         <v>21</v>
@@ -16036,13 +15604,13 @@
     </row>
     <row r="14" spans="1:13">
       <c r="B14" s="157" t="s">
+        <v>534</v>
+      </c>
+      <c r="C14" s="157" t="s">
+        <v>535</v>
+      </c>
+      <c r="D14" s="157" t="s">
         <v>536</v>
-      </c>
-      <c r="C14" s="157" t="s">
-        <v>537</v>
-      </c>
-      <c r="D14" s="157" t="s">
-        <v>538</v>
       </c>
       <c r="E14" s="159">
         <v>1</v>
@@ -16051,10 +15619,10 @@
         <v>241</v>
       </c>
       <c r="I14" s="157" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J14" s="157" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K14" s="157" t="s">
         <v>21</v>
@@ -16068,13 +15636,13 @@
     </row>
     <row r="15" spans="1:13">
       <c r="B15" s="158" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C15" s="158" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D15" s="158" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E15" s="161">
         <v>1</v>
@@ -16083,10 +15651,10 @@
         <v>241</v>
       </c>
       <c r="I15" s="158" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="J15" s="158" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K15" s="158" t="s">
         <v>21</v>
@@ -16100,13 +15668,13 @@
     </row>
     <row r="16" spans="1:13">
       <c r="B16" s="157" t="s">
+        <v>538</v>
+      </c>
+      <c r="C16" s="157" t="s">
+        <v>539</v>
+      </c>
+      <c r="D16" s="157" t="s">
         <v>540</v>
-      </c>
-      <c r="C16" s="157" t="s">
-        <v>541</v>
-      </c>
-      <c r="D16" s="157" t="s">
-        <v>542</v>
       </c>
       <c r="E16" s="159">
         <v>1</v>
@@ -16115,10 +15683,10 @@
         <v>241</v>
       </c>
       <c r="I16" s="157" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J16" s="157" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K16" s="157" t="s">
         <v>21</v>
@@ -16132,13 +15700,13 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="158" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C17" s="158" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D17" s="158" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E17" s="161">
         <v>1</v>
@@ -16147,10 +15715,10 @@
         <v>241</v>
       </c>
       <c r="I17" s="158" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J17" s="158" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K17" s="158" t="s">
         <v>21</v>
@@ -16164,13 +15732,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="157" t="s">
+        <v>542</v>
+      </c>
+      <c r="C18" s="157" t="s">
+        <v>543</v>
+      </c>
+      <c r="D18" s="157" t="s">
         <v>544</v>
-      </c>
-      <c r="C18" s="157" t="s">
-        <v>545</v>
-      </c>
-      <c r="D18" s="157" t="s">
-        <v>546</v>
       </c>
       <c r="E18" s="159">
         <v>1</v>
@@ -16179,10 +15747,10 @@
         <v>241</v>
       </c>
       <c r="I18" s="157" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J18" s="157" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K18" s="157" t="s">
         <v>21</v>
@@ -16196,13 +15764,13 @@
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="158" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C19" s="158" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D19" s="158" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E19" s="161">
         <v>1</v>
@@ -16211,10 +15779,10 @@
         <v>241</v>
       </c>
       <c r="I19" s="158" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="J19" s="158" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K19" s="158" t="s">
         <v>21</v>
@@ -16228,13 +15796,13 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="157" t="s">
+        <v>546</v>
+      </c>
+      <c r="C20" s="157" t="s">
+        <v>547</v>
+      </c>
+      <c r="D20" s="157" t="s">
         <v>548</v>
-      </c>
-      <c r="C20" s="157" t="s">
-        <v>549</v>
-      </c>
-      <c r="D20" s="157" t="s">
-        <v>550</v>
       </c>
       <c r="E20" s="159">
         <v>1</v>
@@ -16243,10 +15811,10 @@
         <v>241</v>
       </c>
       <c r="I20" s="157" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J20" s="157" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K20" s="157" t="s">
         <v>21</v>
@@ -16260,13 +15828,13 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="158" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C21" s="158" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D21" s="158" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E21" s="161">
         <v>1</v>
@@ -16275,10 +15843,10 @@
         <v>241</v>
       </c>
       <c r="I21" s="158" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="J21" s="158" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K21" s="158" t="s">
         <v>21</v>
@@ -16292,13 +15860,13 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="157" t="s">
+        <v>550</v>
+      </c>
+      <c r="C22" s="157" t="s">
+        <v>551</v>
+      </c>
+      <c r="D22" s="157" t="s">
         <v>552</v>
-      </c>
-      <c r="C22" s="157" t="s">
-        <v>553</v>
-      </c>
-      <c r="D22" s="157" t="s">
-        <v>554</v>
       </c>
       <c r="E22" s="159">
         <v>1</v>
@@ -16307,10 +15875,10 @@
         <v>241</v>
       </c>
       <c r="I22" s="157" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J22" s="157" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K22" s="157" t="s">
         <v>21</v>
@@ -16324,13 +15892,13 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="158" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C23" s="158" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D23" s="158" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E23" s="161">
         <v>1</v>
@@ -16339,10 +15907,10 @@
         <v>241</v>
       </c>
       <c r="I23" s="158" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J23" s="158" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="K23" s="158" t="s">
         <v>21</v>
@@ -16356,13 +15924,13 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="157" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C24" s="157" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D24" s="157" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E24" s="159">
         <v>1</v>
@@ -16371,10 +15939,10 @@
         <v>241</v>
       </c>
       <c r="I24" s="157" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J24" s="157" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K24" s="157" t="s">
         <v>21</v>
@@ -16388,13 +15956,13 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="158" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C25" s="158" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D25" s="158" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E25" s="161">
         <v>1</v>
@@ -16403,10 +15971,10 @@
         <v>241</v>
       </c>
       <c r="I25" s="158" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J25" s="158" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K25" s="158" t="s">
         <v>21</v>
@@ -16420,13 +15988,13 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="157" t="s">
+        <v>557</v>
+      </c>
+      <c r="C26" s="157" t="s">
+        <v>558</v>
+      </c>
+      <c r="D26" s="157" t="s">
         <v>559</v>
-      </c>
-      <c r="C26" s="157" t="s">
-        <v>560</v>
-      </c>
-      <c r="D26" s="157" t="s">
-        <v>561</v>
       </c>
       <c r="E26" s="159">
         <v>1</v>
@@ -16435,10 +16003,10 @@
         <v>241</v>
       </c>
       <c r="I26" s="157" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J26" s="157" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K26" s="157" t="s">
         <v>21</v>
@@ -16452,13 +16020,13 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="158" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C27" s="158" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D27" s="158" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E27" s="161">
         <v>1</v>
@@ -16467,10 +16035,10 @@
         <v>241</v>
       </c>
       <c r="I27" s="158" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J27" s="158" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K27" s="158" t="s">
         <v>21</v>
@@ -16484,13 +16052,13 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="157" t="s">
+        <v>561</v>
+      </c>
+      <c r="C28" s="157" t="s">
+        <v>562</v>
+      </c>
+      <c r="D28" s="157" t="s">
         <v>563</v>
-      </c>
-      <c r="C28" s="157" t="s">
-        <v>564</v>
-      </c>
-      <c r="D28" s="157" t="s">
-        <v>565</v>
       </c>
       <c r="E28" s="159">
         <v>1</v>
@@ -16499,10 +16067,10 @@
         <v>241</v>
       </c>
       <c r="I28" s="157" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J28" s="157" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K28" s="157" t="s">
         <v>21</v>
@@ -16516,13 +16084,13 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="158" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C29" s="158" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D29" s="158" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E29" s="161">
         <v>1</v>
@@ -16531,10 +16099,10 @@
         <v>241</v>
       </c>
       <c r="I29" s="158" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J29" s="158" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K29" s="158" t="s">
         <v>21</v>
@@ -16548,13 +16116,13 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="157" t="s">
+        <v>565</v>
+      </c>
+      <c r="C30" s="157" t="s">
+        <v>566</v>
+      </c>
+      <c r="D30" s="157" t="s">
         <v>567</v>
-      </c>
-      <c r="C30" s="157" t="s">
-        <v>568</v>
-      </c>
-      <c r="D30" s="157" t="s">
-        <v>569</v>
       </c>
       <c r="E30" s="159">
         <v>1</v>
@@ -16563,10 +16131,10 @@
         <v>241</v>
       </c>
       <c r="I30" s="157" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J30" s="157" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="K30" s="157" t="s">
         <v>21</v>
@@ -16580,13 +16148,13 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="158" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C31" s="158" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D31" s="158" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E31" s="161">
         <v>1</v>
@@ -16595,10 +16163,10 @@
         <v>241</v>
       </c>
       <c r="I31" s="158" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J31" s="158" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K31" s="158" t="s">
         <v>21</v>
@@ -16612,13 +16180,13 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="157" t="s">
+        <v>569</v>
+      </c>
+      <c r="C32" s="157" t="s">
+        <v>570</v>
+      </c>
+      <c r="D32" s="157" t="s">
         <v>571</v>
-      </c>
-      <c r="C32" s="157" t="s">
-        <v>572</v>
-      </c>
-      <c r="D32" s="157" t="s">
-        <v>573</v>
       </c>
       <c r="E32" s="159">
         <v>1</v>
@@ -16627,10 +16195,10 @@
         <v>241</v>
       </c>
       <c r="I32" s="157" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J32" s="157" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="K32" s="157" t="s">
         <v>21</v>
@@ -16644,13 +16212,13 @@
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="158" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C33" s="158" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D33" s="158" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E33" s="161">
         <v>1</v>
@@ -16659,10 +16227,10 @@
         <v>241</v>
       </c>
       <c r="I33" s="158" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J33" s="158" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K33" s="158" t="s">
         <v>21</v>
@@ -16676,13 +16244,13 @@
     </row>
     <row r="34" spans="2:13">
       <c r="B34" s="157" t="s">
+        <v>573</v>
+      </c>
+      <c r="C34" s="157" t="s">
+        <v>574</v>
+      </c>
+      <c r="D34" s="157" t="s">
         <v>575</v>
-      </c>
-      <c r="C34" s="157" t="s">
-        <v>576</v>
-      </c>
-      <c r="D34" s="157" t="s">
-        <v>577</v>
       </c>
       <c r="E34" s="159">
         <v>1</v>
@@ -16691,10 +16259,10 @@
         <v>241</v>
       </c>
       <c r="I34" s="157" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J34" s="157" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="K34" s="157" t="s">
         <v>21</v>
@@ -16708,13 +16276,13 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="158" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C35" s="158" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D35" s="158" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E35" s="161">
         <v>1</v>
@@ -16723,10 +16291,10 @@
         <v>241</v>
       </c>
       <c r="I35" s="158" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J35" s="158" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="K35" s="158" t="s">
         <v>21</v>
@@ -16740,13 +16308,13 @@
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="157" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C36" s="157" t="s">
         <v>412</v>
       </c>
       <c r="D36" s="157" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E36" s="159">
         <v>1</v>
@@ -16755,10 +16323,10 @@
         <v>241</v>
       </c>
       <c r="I36" s="157" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J36" s="157" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="K36" s="157" t="s">
         <v>21</v>
@@ -16772,10 +16340,10 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="158" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C37" s="158" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D37" s="158" t="s">
         <v>412</v>
@@ -16787,10 +16355,10 @@
         <v>241</v>
       </c>
       <c r="I37" s="158" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J37" s="158" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="K37" s="158" t="s">
         <v>21</v>
@@ -16804,13 +16372,13 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="157" t="s">
+        <v>580</v>
+      </c>
+      <c r="C38" s="157" t="s">
+        <v>581</v>
+      </c>
+      <c r="D38" s="157" t="s">
         <v>582</v>
-      </c>
-      <c r="C38" s="157" t="s">
-        <v>583</v>
-      </c>
-      <c r="D38" s="157" t="s">
-        <v>584</v>
       </c>
       <c r="E38" s="159">
         <v>1</v>
@@ -16819,10 +16387,10 @@
         <v>241</v>
       </c>
       <c r="I38" s="157" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J38" s="157" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K38" s="157" t="s">
         <v>21</v>
@@ -16836,13 +16404,13 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="158" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C39" s="158" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D39" s="158" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E39" s="161">
         <v>1</v>
@@ -16851,10 +16419,10 @@
         <v>241</v>
       </c>
       <c r="I39" s="158" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J39" s="158" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="K39" s="158" t="s">
         <v>21</v>
@@ -16868,13 +16436,13 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="157" t="s">
+        <v>584</v>
+      </c>
+      <c r="C40" s="157" t="s">
+        <v>585</v>
+      </c>
+      <c r="D40" s="157" t="s">
         <v>586</v>
-      </c>
-      <c r="C40" s="157" t="s">
-        <v>587</v>
-      </c>
-      <c r="D40" s="157" t="s">
-        <v>588</v>
       </c>
       <c r="E40" s="159">
         <v>1</v>
@@ -16883,10 +16451,10 @@
         <v>241</v>
       </c>
       <c r="I40" s="157" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J40" s="157" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="K40" s="157" t="s">
         <v>21</v>
@@ -16900,13 +16468,13 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="158" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C41" s="158" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D41" s="158" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E41" s="161">
         <v>1</v>
@@ -16915,10 +16483,10 @@
         <v>241</v>
       </c>
       <c r="I41" s="158" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J41" s="158" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="K41" s="158" t="s">
         <v>21</v>
@@ -16932,13 +16500,13 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="157" t="s">
+        <v>588</v>
+      </c>
+      <c r="C42" s="157" t="s">
+        <v>589</v>
+      </c>
+      <c r="D42" s="157" t="s">
         <v>590</v>
-      </c>
-      <c r="C42" s="157" t="s">
-        <v>591</v>
-      </c>
-      <c r="D42" s="157" t="s">
-        <v>592</v>
       </c>
       <c r="E42" s="159">
         <v>1</v>
@@ -16947,10 +16515,10 @@
         <v>241</v>
       </c>
       <c r="I42" s="157" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J42" s="157" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="K42" s="157" t="s">
         <v>21</v>
@@ -16964,13 +16532,13 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="158" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C43" s="158" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D43" s="158" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E43" s="161">
         <v>1</v>
@@ -16979,10 +16547,10 @@
         <v>241</v>
       </c>
       <c r="I43" s="158" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J43" s="158" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="K43" s="158" t="s">
         <v>21</v>
@@ -16996,13 +16564,13 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="157" t="s">
+        <v>592</v>
+      </c>
+      <c r="C44" s="157" t="s">
+        <v>593</v>
+      </c>
+      <c r="D44" s="157" t="s">
         <v>594</v>
-      </c>
-      <c r="C44" s="157" t="s">
-        <v>595</v>
-      </c>
-      <c r="D44" s="157" t="s">
-        <v>596</v>
       </c>
       <c r="E44" s="159">
         <v>1</v>
@@ -17011,10 +16579,10 @@
         <v>241</v>
       </c>
       <c r="I44" s="157" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="J44" s="157" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="K44" s="157" t="s">
         <v>21</v>
@@ -17028,13 +16596,13 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="158" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C45" s="158" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D45" s="158" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E45" s="161">
         <v>1</v>
@@ -17043,10 +16611,10 @@
         <v>241</v>
       </c>
       <c r="I45" s="158" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J45" s="158" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="K45" s="158" t="s">
         <v>21</v>
@@ -17060,13 +16628,13 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="157" t="s">
+        <v>596</v>
+      </c>
+      <c r="C46" s="157" t="s">
+        <v>597</v>
+      </c>
+      <c r="D46" s="157" t="s">
         <v>598</v>
-      </c>
-      <c r="C46" s="157" t="s">
-        <v>599</v>
-      </c>
-      <c r="D46" s="157" t="s">
-        <v>600</v>
       </c>
       <c r="E46" s="159">
         <v>1</v>
@@ -17075,10 +16643,10 @@
         <v>241</v>
       </c>
       <c r="I46" s="157" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="J46" s="157" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="K46" s="157" t="s">
         <v>21</v>
@@ -17092,13 +16660,13 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="158" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C47" s="158" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D47" s="158" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E47" s="161">
         <v>1</v>
@@ -17107,10 +16675,10 @@
         <v>241</v>
       </c>
       <c r="I47" s="158" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="J47" s="158" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="K47" s="158" t="s">
         <v>21</v>
@@ -17124,13 +16692,13 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="157" t="s">
+        <v>600</v>
+      </c>
+      <c r="C48" s="157" t="s">
+        <v>601</v>
+      </c>
+      <c r="D48" s="157" t="s">
         <v>602</v>
-      </c>
-      <c r="C48" s="157" t="s">
-        <v>603</v>
-      </c>
-      <c r="D48" s="157" t="s">
-        <v>604</v>
       </c>
       <c r="E48" s="159">
         <v>1</v>
@@ -17139,10 +16707,10 @@
         <v>241</v>
       </c>
       <c r="I48" s="157" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J48" s="157" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="K48" s="157" t="s">
         <v>21</v>
@@ -17156,13 +16724,13 @@
     </row>
     <row r="49" spans="2:13">
       <c r="B49" s="158" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C49" s="158" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D49" s="158" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E49" s="161">
         <v>1</v>
@@ -17171,10 +16739,10 @@
         <v>241</v>
       </c>
       <c r="I49" s="158" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J49" s="158" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="K49" s="158" t="s">
         <v>21</v>
@@ -17188,13 +16756,13 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="157" t="s">
+        <v>604</v>
+      </c>
+      <c r="C50" s="157" t="s">
+        <v>605</v>
+      </c>
+      <c r="D50" s="157" t="s">
         <v>606</v>
-      </c>
-      <c r="C50" s="157" t="s">
-        <v>607</v>
-      </c>
-      <c r="D50" s="157" t="s">
-        <v>608</v>
       </c>
       <c r="E50" s="159">
         <v>1</v>
@@ -17203,10 +16771,10 @@
         <v>241</v>
       </c>
       <c r="I50" s="157" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J50" s="157" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="K50" s="157" t="s">
         <v>21</v>
@@ -17220,13 +16788,13 @@
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="158" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C51" s="158" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D51" s="158" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E51" s="161">
         <v>1</v>
@@ -17235,10 +16803,10 @@
         <v>241</v>
       </c>
       <c r="I51" s="158" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="J51" s="158" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="K51" s="158" t="s">
         <v>21</v>
@@ -17252,13 +16820,13 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="157" t="s">
+        <v>608</v>
+      </c>
+      <c r="C52" s="157" t="s">
+        <v>609</v>
+      </c>
+      <c r="D52" s="157" t="s">
         <v>610</v>
-      </c>
-      <c r="C52" s="157" t="s">
-        <v>611</v>
-      </c>
-      <c r="D52" s="157" t="s">
-        <v>612</v>
       </c>
       <c r="E52" s="159">
         <v>1</v>
@@ -17267,10 +16835,10 @@
         <v>241</v>
       </c>
       <c r="I52" s="157" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J52" s="157" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="K52" s="157" t="s">
         <v>21</v>
@@ -17284,13 +16852,13 @@
     </row>
     <row r="53" spans="2:13">
       <c r="B53" s="158" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C53" s="158" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D53" s="158" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E53" s="161">
         <v>1</v>
@@ -17299,10 +16867,10 @@
         <v>241</v>
       </c>
       <c r="I53" s="158" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J53" s="158" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="K53" s="158" t="s">
         <v>21</v>
@@ -17316,13 +16884,13 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="157" t="s">
+        <v>612</v>
+      </c>
+      <c r="C54" s="157" t="s">
+        <v>613</v>
+      </c>
+      <c r="D54" s="157" t="s">
         <v>614</v>
-      </c>
-      <c r="C54" s="157" t="s">
-        <v>615</v>
-      </c>
-      <c r="D54" s="157" t="s">
-        <v>616</v>
       </c>
       <c r="E54" s="159">
         <v>1</v>
@@ -17331,10 +16899,10 @@
         <v>241</v>
       </c>
       <c r="I54" s="157" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J54" s="157" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="K54" s="157" t="s">
         <v>21</v>
@@ -17348,13 +16916,13 @@
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="158" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C55" s="158" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D55" s="158" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E55" s="161">
         <v>1</v>
@@ -17363,10 +16931,10 @@
         <v>241</v>
       </c>
       <c r="I55" s="158" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J55" s="158" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="K55" s="158" t="s">
         <v>21</v>
@@ -17380,13 +16948,13 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="157" t="s">
+        <v>616</v>
+      </c>
+      <c r="C56" s="157" t="s">
+        <v>617</v>
+      </c>
+      <c r="D56" s="157" t="s">
         <v>618</v>
-      </c>
-      <c r="C56" s="157" t="s">
-        <v>619</v>
-      </c>
-      <c r="D56" s="157" t="s">
-        <v>620</v>
       </c>
       <c r="E56" s="159">
         <v>1</v>
@@ -17395,10 +16963,10 @@
         <v>241</v>
       </c>
       <c r="I56" s="157" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J56" s="157" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="K56" s="157" t="s">
         <v>21</v>
@@ -17412,13 +16980,13 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="158" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C57" s="158" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D57" s="158" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E57" s="161">
         <v>1</v>
@@ -17427,10 +16995,10 @@
         <v>241</v>
       </c>
       <c r="I57" s="158" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="J57" s="158" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="K57" s="158" t="s">
         <v>21</v>
@@ -17444,13 +17012,13 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="157" t="s">
+        <v>620</v>
+      </c>
+      <c r="C58" s="157" t="s">
+        <v>621</v>
+      </c>
+      <c r="D58" s="157" t="s">
         <v>622</v>
-      </c>
-      <c r="C58" s="157" t="s">
-        <v>623</v>
-      </c>
-      <c r="D58" s="157" t="s">
-        <v>624</v>
       </c>
       <c r="E58" s="159">
         <v>1</v>
@@ -17459,10 +17027,10 @@
         <v>241</v>
       </c>
       <c r="I58" s="157" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J58" s="157" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="K58" s="157" t="s">
         <v>21</v>
@@ -17476,13 +17044,13 @@
     </row>
     <row r="59" spans="2:13">
       <c r="B59" s="158" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C59" s="158" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D59" s="158" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E59" s="161">
         <v>1</v>
@@ -17491,10 +17059,10 @@
         <v>241</v>
       </c>
       <c r="I59" s="158" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="J59" s="158" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="K59" s="158" t="s">
         <v>21</v>
@@ -17508,13 +17076,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="157" t="s">
+        <v>624</v>
+      </c>
+      <c r="C60" s="157" t="s">
+        <v>625</v>
+      </c>
+      <c r="D60" s="157" t="s">
         <v>626</v>
-      </c>
-      <c r="C60" s="157" t="s">
-        <v>627</v>
-      </c>
-      <c r="D60" s="157" t="s">
-        <v>628</v>
       </c>
       <c r="E60" s="159">
         <v>1</v>
@@ -17523,10 +17091,10 @@
         <v>241</v>
       </c>
       <c r="I60" s="157" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="J60" s="157" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="K60" s="157" t="s">
         <v>21</v>
@@ -17540,13 +17108,13 @@
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="158" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C61" s="158" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D61" s="158" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E61" s="161">
         <v>1</v>
@@ -17555,10 +17123,10 @@
         <v>241</v>
       </c>
       <c r="I61" s="158" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J61" s="158" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="K61" s="158" t="s">
         <v>21</v>
@@ -17572,13 +17140,13 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="157" t="s">
+        <v>628</v>
+      </c>
+      <c r="C62" s="157" t="s">
+        <v>629</v>
+      </c>
+      <c r="D62" s="157" t="s">
         <v>630</v>
-      </c>
-      <c r="C62" s="157" t="s">
-        <v>631</v>
-      </c>
-      <c r="D62" s="157" t="s">
-        <v>632</v>
       </c>
       <c r="E62" s="159">
         <v>1</v>
@@ -17587,10 +17155,10 @@
         <v>241</v>
       </c>
       <c r="I62" s="157" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="J62" s="157" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="K62" s="157" t="s">
         <v>21</v>
@@ -17604,13 +17172,13 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="158" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C63" s="158" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D63" s="158" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E63" s="161">
         <v>1</v>
@@ -17619,10 +17187,10 @@
         <v>241</v>
       </c>
       <c r="I63" s="158" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="J63" s="158" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="K63" s="158" t="s">
         <v>21</v>
@@ -17636,13 +17204,13 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="157" t="s">
+        <v>632</v>
+      </c>
+      <c r="C64" s="157" t="s">
+        <v>633</v>
+      </c>
+      <c r="D64" s="157" t="s">
         <v>634</v>
-      </c>
-      <c r="C64" s="157" t="s">
-        <v>635</v>
-      </c>
-      <c r="D64" s="157" t="s">
-        <v>636</v>
       </c>
       <c r="E64" s="159">
         <v>1</v>
@@ -17651,10 +17219,10 @@
         <v>241</v>
       </c>
       <c r="I64" s="157" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J64" s="157" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="K64" s="157" t="s">
         <v>21</v>
@@ -17668,13 +17236,13 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="158" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C65" s="158" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D65" s="158" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E65" s="161">
         <v>1</v>
@@ -17683,10 +17251,10 @@
         <v>241</v>
       </c>
       <c r="I65" s="158" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="J65" s="158" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="K65" s="158" t="s">
         <v>21</v>
@@ -17700,13 +17268,13 @@
     </row>
     <row r="66" spans="2:13">
       <c r="B66" s="157" t="s">
+        <v>636</v>
+      </c>
+      <c r="C66" s="157" t="s">
+        <v>637</v>
+      </c>
+      <c r="D66" s="157" t="s">
         <v>638</v>
-      </c>
-      <c r="C66" s="157" t="s">
-        <v>639</v>
-      </c>
-      <c r="D66" s="157" t="s">
-        <v>640</v>
       </c>
       <c r="E66" s="159">
         <v>1</v>
@@ -17715,10 +17283,10 @@
         <v>241</v>
       </c>
       <c r="I66" s="157" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="J66" s="157" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="K66" s="157" t="s">
         <v>21</v>
@@ -17732,13 +17300,13 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="158" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C67" s="158" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D67" s="158" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E67" s="161">
         <v>1</v>
@@ -17747,10 +17315,10 @@
         <v>241</v>
       </c>
       <c r="I67" s="158" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="J67" s="158" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="K67" s="158" t="s">
         <v>21</v>
@@ -17764,13 +17332,13 @@
     </row>
     <row r="68" spans="2:13">
       <c r="B68" s="157" t="s">
+        <v>640</v>
+      </c>
+      <c r="C68" s="157" t="s">
+        <v>641</v>
+      </c>
+      <c r="D68" s="157" t="s">
         <v>642</v>
-      </c>
-      <c r="C68" s="157" t="s">
-        <v>643</v>
-      </c>
-      <c r="D68" s="157" t="s">
-        <v>644</v>
       </c>
       <c r="E68" s="159">
         <v>1</v>
@@ -17779,10 +17347,10 @@
         <v>241</v>
       </c>
       <c r="I68" s="157" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J68" s="157" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="K68" s="157" t="s">
         <v>21</v>
@@ -17796,13 +17364,13 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="158" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C69" s="158" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D69" s="158" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E69" s="161">
         <v>1</v>
@@ -17811,10 +17379,10 @@
         <v>241</v>
       </c>
       <c r="I69" s="158" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="J69" s="158" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="K69" s="158" t="s">
         <v>21</v>
@@ -17828,13 +17396,13 @@
     </row>
     <row r="70" spans="2:13">
       <c r="B70" s="157" t="s">
+        <v>644</v>
+      </c>
+      <c r="C70" s="157" t="s">
+        <v>645</v>
+      </c>
+      <c r="D70" s="157" t="s">
         <v>646</v>
-      </c>
-      <c r="C70" s="157" t="s">
-        <v>647</v>
-      </c>
-      <c r="D70" s="157" t="s">
-        <v>648</v>
       </c>
       <c r="E70" s="159">
         <v>1</v>
@@ -17843,10 +17411,10 @@
         <v>241</v>
       </c>
       <c r="I70" s="157" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="J70" s="157" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="K70" s="157" t="s">
         <v>21</v>
@@ -17860,13 +17428,13 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="158" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C71" s="158" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D71" s="158" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E71" s="161">
         <v>1</v>
@@ -17875,10 +17443,10 @@
         <v>241</v>
       </c>
       <c r="I71" s="158" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="J71" s="158" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="K71" s="158" t="s">
         <v>21</v>
@@ -17892,13 +17460,13 @@
     </row>
     <row r="72" spans="2:13">
       <c r="B72" s="157" t="s">
+        <v>648</v>
+      </c>
+      <c r="C72" s="157" t="s">
+        <v>649</v>
+      </c>
+      <c r="D72" s="157" t="s">
         <v>650</v>
-      </c>
-      <c r="C72" s="157" t="s">
-        <v>651</v>
-      </c>
-      <c r="D72" s="157" t="s">
-        <v>652</v>
       </c>
       <c r="E72" s="159">
         <v>1</v>
@@ -17907,10 +17475,10 @@
         <v>241</v>
       </c>
       <c r="I72" s="157" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="J72" s="157" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="K72" s="157" t="s">
         <v>21</v>
@@ -17924,13 +17492,13 @@
     </row>
     <row r="73" spans="2:13">
       <c r="B73" s="158" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C73" s="158" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D73" s="158" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E73" s="161">
         <v>1</v>
@@ -17939,10 +17507,10 @@
         <v>241</v>
       </c>
       <c r="I73" s="158" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J73" s="158" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="K73" s="158" t="s">
         <v>21</v>
@@ -17956,13 +17524,13 @@
     </row>
     <row r="74" spans="2:13">
       <c r="B74" s="157" t="s">
+        <v>652</v>
+      </c>
+      <c r="C74" s="157" t="s">
+        <v>653</v>
+      </c>
+      <c r="D74" s="157" t="s">
         <v>654</v>
-      </c>
-      <c r="C74" s="157" t="s">
-        <v>655</v>
-      </c>
-      <c r="D74" s="157" t="s">
-        <v>656</v>
       </c>
       <c r="E74" s="159">
         <v>1</v>
@@ -17971,10 +17539,10 @@
         <v>241</v>
       </c>
       <c r="I74" s="157" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="J74" s="157" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="K74" s="157" t="s">
         <v>21</v>
@@ -17988,13 +17556,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="158" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C75" s="158" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D75" s="158" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E75" s="161">
         <v>1</v>
@@ -18003,10 +17571,10 @@
         <v>241</v>
       </c>
       <c r="I75" s="158" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="J75" s="158" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="K75" s="158" t="s">
         <v>21</v>
@@ -18020,13 +17588,13 @@
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="157" t="s">
+        <v>656</v>
+      </c>
+      <c r="C76" s="157" t="s">
+        <v>657</v>
+      </c>
+      <c r="D76" s="157" t="s">
         <v>658</v>
-      </c>
-      <c r="C76" s="157" t="s">
-        <v>659</v>
-      </c>
-      <c r="D76" s="157" t="s">
-        <v>660</v>
       </c>
       <c r="E76" s="159">
         <v>1</v>
@@ -18035,10 +17603,10 @@
         <v>241</v>
       </c>
       <c r="I76" s="157" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J76" s="157" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="K76" s="157" t="s">
         <v>21</v>
@@ -18052,13 +17620,13 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="158" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C77" s="158" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D77" s="158" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E77" s="161">
         <v>1</v>
@@ -18067,10 +17635,10 @@
         <v>241</v>
       </c>
       <c r="I77" s="158" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="J77" s="158" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K77" s="158" t="s">
         <v>21</v>
@@ -18084,13 +17652,13 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="157" t="s">
+        <v>660</v>
+      </c>
+      <c r="C78" s="157" t="s">
+        <v>661</v>
+      </c>
+      <c r="D78" s="157" t="s">
         <v>662</v>
-      </c>
-      <c r="C78" s="157" t="s">
-        <v>663</v>
-      </c>
-      <c r="D78" s="157" t="s">
-        <v>664</v>
       </c>
       <c r="E78" s="159">
         <v>1</v>
@@ -18099,10 +17667,10 @@
         <v>241</v>
       </c>
       <c r="I78" s="157" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="J78" s="157" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="K78" s="157" t="s">
         <v>21</v>
@@ -18116,13 +17684,13 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="158" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C79" s="158" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D79" s="158" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E79" s="161">
         <v>1</v>
@@ -18131,10 +17699,10 @@
         <v>241</v>
       </c>
       <c r="I79" s="158" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J79" s="158" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="K79" s="158" t="s">
         <v>21</v>
@@ -18148,13 +17716,13 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="157" t="s">
+        <v>664</v>
+      </c>
+      <c r="C80" s="157" t="s">
+        <v>665</v>
+      </c>
+      <c r="D80" s="157" t="s">
         <v>666</v>
-      </c>
-      <c r="C80" s="157" t="s">
-        <v>667</v>
-      </c>
-      <c r="D80" s="157" t="s">
-        <v>668</v>
       </c>
       <c r="E80" s="159">
         <v>1</v>
@@ -18163,10 +17731,10 @@
         <v>241</v>
       </c>
       <c r="I80" s="157" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J80" s="157" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="K80" s="157" t="s">
         <v>21</v>
@@ -18180,13 +17748,13 @@
     </row>
     <row r="81" spans="2:13">
       <c r="B81" s="158" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C81" s="158" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D81" s="158" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E81" s="161">
         <v>1</v>
@@ -18195,10 +17763,10 @@
         <v>241</v>
       </c>
       <c r="I81" s="158" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J81" s="158" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="K81" s="158" t="s">
         <v>21</v>
@@ -18212,13 +17780,13 @@
     </row>
     <row r="82" spans="2:13">
       <c r="B82" s="157" t="s">
+        <v>668</v>
+      </c>
+      <c r="C82" s="157" t="s">
+        <v>669</v>
+      </c>
+      <c r="D82" s="157" t="s">
         <v>670</v>
-      </c>
-      <c r="C82" s="157" t="s">
-        <v>671</v>
-      </c>
-      <c r="D82" s="157" t="s">
-        <v>672</v>
       </c>
       <c r="E82" s="159">
         <v>1</v>
@@ -18227,10 +17795,10 @@
         <v>241</v>
       </c>
       <c r="I82" s="157" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="J82" s="157" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="K82" s="157" t="s">
         <v>21</v>
@@ -18244,13 +17812,13 @@
     </row>
     <row r="83" spans="2:13">
       <c r="B83" s="158" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C83" s="158" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D83" s="158" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E83" s="161">
         <v>1</v>
@@ -18259,10 +17827,10 @@
         <v>241</v>
       </c>
       <c r="I83" s="158" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="J83" s="158" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="K83" s="158" t="s">
         <v>21</v>
@@ -18276,13 +17844,13 @@
     </row>
     <row r="84" spans="2:13">
       <c r="B84" s="157" t="s">
+        <v>672</v>
+      </c>
+      <c r="C84" s="157" t="s">
+        <v>673</v>
+      </c>
+      <c r="D84" s="157" t="s">
         <v>674</v>
-      </c>
-      <c r="C84" s="157" t="s">
-        <v>675</v>
-      </c>
-      <c r="D84" s="157" t="s">
-        <v>676</v>
       </c>
       <c r="E84" s="159">
         <v>1</v>
@@ -18291,10 +17859,10 @@
         <v>241</v>
       </c>
       <c r="I84" s="157" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J84" s="157" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="K84" s="157" t="s">
         <v>21</v>
@@ -18308,13 +17876,13 @@
     </row>
     <row r="85" spans="2:13">
       <c r="B85" s="158" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C85" s="158" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D85" s="158" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E85" s="161">
         <v>1</v>
@@ -18323,10 +17891,10 @@
         <v>241</v>
       </c>
       <c r="I85" s="158" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="J85" s="158" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K85" s="158" t="s">
         <v>21</v>
@@ -18340,13 +17908,13 @@
     </row>
     <row r="86" spans="2:13">
       <c r="B86" s="157" t="s">
+        <v>676</v>
+      </c>
+      <c r="C86" s="157" t="s">
+        <v>677</v>
+      </c>
+      <c r="D86" s="157" t="s">
         <v>678</v>
-      </c>
-      <c r="C86" s="157" t="s">
-        <v>679</v>
-      </c>
-      <c r="D86" s="157" t="s">
-        <v>680</v>
       </c>
       <c r="E86" s="159">
         <v>1</v>
@@ -18355,10 +17923,10 @@
         <v>241</v>
       </c>
       <c r="I86" s="157" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J86" s="157" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="K86" s="157" t="s">
         <v>21</v>
@@ -18372,13 +17940,13 @@
     </row>
     <row r="87" spans="2:13">
       <c r="B87" s="158" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C87" s="158" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D87" s="158" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E87" s="161">
         <v>1</v>
@@ -18387,10 +17955,10 @@
         <v>241</v>
       </c>
       <c r="I87" s="158" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J87" s="158" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="K87" s="158" t="s">
         <v>21</v>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0481E28-B96E-46A0-9A1A-D17ABB48895A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5AA08FB-741F-4280-B689-712CF055D74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,24 +853,120 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_014</t>
   </si>
   <si>
@@ -883,166 +979,124 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
+  </si>
+  <si>
+    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
     <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
   </si>
   <si>
     <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
   </si>
   <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
     <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
   </si>
   <si>
     <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
   </si>
   <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
-  </si>
-  <si>
-    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_017</t>
@@ -1051,46 +1105,46 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_009</t>
@@ -1105,112 +1159,112 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
     <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
@@ -1222,60 +1276,6 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
@@ -1294,6 +1294,18 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_007</t>
   </si>
   <si>
@@ -1312,36 +1324,24 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
@@ -1354,6 +1354,18 @@
     <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
@@ -1372,31 +1384,19 @@
     <t>e_PL1-400_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
     <t>e_w175406958-400_POL,e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7160,7 +7160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8742F136-877B-48A9-9B8A-CBDF59428AB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF893FF-99DC-487B-9345-5568EAC4367E}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7398,16 +7398,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99648087644372252</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB11">
-        <v>64.517265198419722</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -7440,10 +7440,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99776911581804295</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP11">
-        <v>40.899543335879912</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7544,16 +7544,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99621535905375425</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB12">
-        <v>69.385084014505708</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -7586,10 +7586,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99802303154782224</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP12">
-        <v>36.244421623259619</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7690,16 +7690,16 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.99801094175818605</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB13">
-        <v>36.466067766588218</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
@@ -7732,10 +7732,10 @@
         <v>350</v>
       </c>
       <c r="AO13">
-        <v>0.99714358927215652</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP13">
-        <v>52.367530010463909</v>
+        <v>36.244421623259619</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7768,10 +7768,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.99603343715055259</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD13">
-        <v>72.720318906536249</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7836,16 +7836,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99909366739195871</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB14">
-        <v>16.616097814091063</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7878,10 +7878,10 @@
         <v>352</v>
       </c>
       <c r="AO14">
-        <v>0.99845079995590791</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP14">
-        <v>28.402000808355538</v>
+        <v>52.367530010463909</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7914,10 +7914,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99255696761939116</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD14">
-        <v>136.4555936444961</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7982,16 +7982,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99860106452186825</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB15">
-        <v>25.647150432415483</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -8024,10 +8024,10 @@
         <v>354</v>
       </c>
       <c r="AO15">
-        <v>0.9963019969989696</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP15">
-        <v>67.796721685557472</v>
+        <v>28.402000808355538</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8060,10 +8060,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99615776238359954</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD15">
-        <v>70.441022967342263</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8128,16 +8128,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99775856069920277</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB16">
-        <v>41.093053847949164</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8170,10 +8170,10 @@
         <v>356</v>
       </c>
       <c r="AO16">
-        <v>0.99730422320290779</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP16">
-        <v>49.422574613357185</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8206,10 +8206,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99399718012600935</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD16">
-        <v>110.05169768982766</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8274,16 +8274,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99763459325217896</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB17">
-        <v>43.365790376719588</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -8316,10 +8316,10 @@
         <v>358</v>
       </c>
       <c r="AO17">
-        <v>0.99805709209211746</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP17">
-        <v>35.619978311179104</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8352,10 +8352,10 @@
         <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.9932866968373224</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD17">
-        <v>123.07722464908932</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8420,16 +8420,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.99733507264559695</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB18">
-        <v>48.857001497390002</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -8462,10 +8462,10 @@
         <v>360</v>
       </c>
       <c r="AO18">
-        <v>0.99873239758997023</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP18">
-        <v>23.239377517213022</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8498,10 +8498,10 @@
         <v>419</v>
       </c>
       <c r="BC18">
-        <v>0.99644388872049838</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD18">
-        <v>65.195373457529499</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8566,16 +8566,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99583365539385327</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB19">
-        <v>76.382984446022675</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -8608,10 +8608,10 @@
         <v>362</v>
       </c>
       <c r="AO19">
-        <v>0.99635146162488653</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP19">
-        <v>66.889870210414614</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8641,13 +8641,13 @@
         <v>420</v>
       </c>
       <c r="BB19" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="BC19">
-        <v>0.99383395234396599</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD19">
-        <v>113.04420702728957</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8712,16 +8712,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99875154162789404</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB20">
-        <v>22.888403488609324</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8751,13 +8751,13 @@
         <v>363</v>
       </c>
       <c r="AN20" t="s">
-        <v>286</v>
+        <v>364</v>
       </c>
       <c r="AO20">
-        <v>0.99586212495478665</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP20">
-        <v>75.861042495577635</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8784,16 +8784,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
+        <v>421</v>
+      </c>
+      <c r="BB20" t="s">
         <v>422</v>
       </c>
-      <c r="BB20" t="s">
-        <v>419</v>
-      </c>
       <c r="BC20">
-        <v>0.99564789206089888</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD20">
-        <v>79.788645550187297</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8858,16 +8858,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99812712894455979</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB21">
-        <v>34.335969349736395</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8894,16 +8894,16 @@
         <v>325</v>
       </c>
       <c r="AM21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN21" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO21">
-        <v>0.99826576737141715</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP21">
-        <v>31.794264857351436</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8968,16 +8968,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99834158364926728</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB22">
-        <v>30.404299763434018</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -9004,16 +9004,16 @@
         <v>327</v>
       </c>
       <c r="AM22" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN22" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO22">
-        <v>0.99871360797890252</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP22">
-        <v>23.583853720120768</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9078,16 +9078,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.9987403722896917</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB23">
-        <v>23.093174688985375</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9114,16 +9114,16 @@
         <v>329</v>
       </c>
       <c r="AM23" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN23" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO23">
-        <v>0.99641308487583879</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP23">
-        <v>65.760110609622657</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9188,16 +9188,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99572127940552169</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB24">
-        <v>78.443210898768598</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9224,16 +9224,16 @@
         <v>331</v>
       </c>
       <c r="AM24" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO24">
-        <v>0.99449756685866841</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP24">
-        <v>100.87794092441324</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9334,16 +9334,16 @@
         <v>333</v>
       </c>
       <c r="AM25" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN25" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO25">
-        <v>0.99883902037019667</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP25">
-        <v>21.284626546395259</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9408,16 +9408,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99505524223378883</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB26">
-        <v>90.653892380538664</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9444,16 +9444,16 @@
         <v>335</v>
       </c>
       <c r="AM26" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO26">
-        <v>0.99521984547821263</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP26">
-        <v>87.636166232768815</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9518,16 +9518,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99729953359766199</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB27">
-        <v>49.508550709529651</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9554,16 +9554,16 @@
         <v>337</v>
       </c>
       <c r="AM27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN27" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO27">
-        <v>0.99749126227646956</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP27">
-        <v>45.993524931390482</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9628,16 +9628,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99511607748745434</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB28">
-        <v>89.538579396670116</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9664,16 +9664,16 @@
         <v>339</v>
       </c>
       <c r="AM28" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO28">
-        <v>0.99807543246352515</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP28">
-        <v>35.283738168705199</v>
+        <v>66.889870210414614</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9738,16 +9738,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99692898913090644</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB29">
-        <v>56.301865933381954</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -9774,16 +9774,16 @@
         <v>341</v>
       </c>
       <c r="AM29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN29" t="s">
-        <v>381</v>
+        <v>301</v>
       </c>
       <c r="AO29">
-        <v>0.99653588726932718</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP29">
-        <v>63.508733395668145</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9848,16 +9848,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Z30" t="s">
         <v>304</v>
       </c>
       <c r="AA30">
-        <v>0.99839233674974392</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB30">
-        <v>29.473826254695162</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9902,7 +9902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8075810A-E1A7-473A-822C-B0F232B50D42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062937C3-53A2-4D99-BA46-09CCC3F71462}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10014,7 +10014,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10047,7 +10047,7 @@
         <v>463</v>
       </c>
       <c r="X11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10082,7 +10082,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10150,7 +10150,7 @@
         <v>427</v>
       </c>
       <c r="K13" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10183,7 +10183,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10251,7 +10251,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10286,7 +10286,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10319,7 +10319,7 @@
         <v>471</v>
       </c>
       <c r="X15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10354,7 +10354,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10387,7 +10387,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10422,7 +10422,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10455,7 +10455,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10490,7 +10490,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10523,7 +10523,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10558,7 +10558,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10591,7 +10591,7 @@
         <v>479</v>
       </c>
       <c r="X19" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10626,7 +10626,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10694,7 +10694,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10729,7 +10729,7 @@
         <v>445</v>
       </c>
       <c r="K22" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10764,7 +10764,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10799,7 +10799,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10834,7 +10834,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10869,7 +10869,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10904,7 +10904,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10974,7 +10974,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -11009,7 +11009,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11024,7 +11024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05477CAD-889D-4FFD-86AC-0787001CEFF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945D3ECB-43BA-4C90-92A2-B5954FD850F2}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14526,7 +14526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BA47ED-C03A-432F-99F0-B16FCB24D134}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC01801-A874-4DF9-B43A-CAF76DE4E8D1}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5AA08FB-741F-4280-B689-712CF055D74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75D0CA02-E445-4E25-9666-05FA65CB8FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,196 +853,286 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_016</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
+  </si>
+  <si>
+    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
+  </si>
+  <si>
     <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
   </si>
   <si>
-    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
-  </si>
-  <si>
-    <t>e_w177749653-220_POL,e_w179279860-220_POL,e_w336990960-220_POL,e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
     <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
   </si>
   <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_013</t>
@@ -1057,54 +1147,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_012</t>
   </si>
   <si>
@@ -1117,52 +1159,97 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_007</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
@@ -1177,54 +1264,6 @@
     <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>e_PL40-220_POL,e_w111615226-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
@@ -1237,49 +1276,40 @@
     <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
     <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_010</t>
@@ -1294,34 +1324,10 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_005</t>
@@ -1336,10 +1342,34 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_w255314292_POL,e_PL1-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
@@ -1354,34 +1384,10 @@
     <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL,e_PL1-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL</t>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL,e_w255314292_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
@@ -1391,12 +1397,6 @@
   </si>
   <si>
     <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL,e_w255314292_POL</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7160,7 +7160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF893FF-99DC-487B-9345-5568EAC4367E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874DBE8D-DF89-4469-A734-BB13B5240615}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7398,16 +7398,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99572127940552169</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB11">
-        <v>78.443210898768598</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -7440,10 +7440,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99883902037019667</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP11">
-        <v>21.284626546395259</v>
+        <v>36.244421623259619</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7476,10 +7476,10 @@
         <v>405</v>
       </c>
       <c r="BC11">
-        <v>0.99609037037675463</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD11">
-        <v>71.676543092831025</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7544,16 +7544,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99511607748745434</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB12">
-        <v>89.538579396670116</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -7586,10 +7586,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99521984547821263</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP12">
-        <v>87.636166232768815</v>
+        <v>52.367530010463909</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7622,10 +7622,10 @@
         <v>407</v>
       </c>
       <c r="BC12">
-        <v>0.99353710926584593</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD12">
-        <v>118.48633012615811</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7690,16 +7690,16 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.99733507264559695</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB13">
-        <v>48.857001497390002</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
@@ -7732,10 +7732,10 @@
         <v>350</v>
       </c>
       <c r="AO13">
-        <v>0.99802303154782224</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP13">
-        <v>36.244421623259619</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7768,10 +7768,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.99383395234396599</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD13">
-        <v>113.04420702728957</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7836,16 +7836,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99583365539385327</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB14">
-        <v>76.382984446022675</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7878,10 +7878,10 @@
         <v>352</v>
       </c>
       <c r="AO14">
-        <v>0.99714358927215652</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP14">
-        <v>52.367530010463909</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7914,10 +7914,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99564789206089888</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD14">
-        <v>79.788645550187297</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7982,16 +7982,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99875154162789404</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB15">
-        <v>22.888403488609324</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -8024,10 +8024,10 @@
         <v>354</v>
       </c>
       <c r="AO15">
-        <v>0.99845079995590791</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP15">
-        <v>28.402000808355538</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8060,10 +8060,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99603343715055259</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD15">
-        <v>72.720318906536249</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8128,16 +8128,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99812712894455979</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB16">
-        <v>34.335969349736395</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8170,10 +8170,10 @@
         <v>356</v>
       </c>
       <c r="AO16">
-        <v>0.9963019969989696</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP16">
-        <v>67.796721685557472</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8206,10 +8206,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99255696761939116</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD16">
-        <v>136.4555936444961</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8274,16 +8274,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99834158364926728</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB17">
-        <v>30.404299763434018</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -8316,10 +8316,10 @@
         <v>358</v>
       </c>
       <c r="AO17">
-        <v>0.99873239758997023</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP17">
-        <v>23.239377517213022</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8352,10 +8352,10 @@
         <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.99615776238359954</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD17">
-        <v>70.441022967342263</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8420,16 +8420,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.9987403722896917</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB18">
-        <v>23.093174688985375</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -8459,13 +8459,13 @@
         <v>359</v>
       </c>
       <c r="AN18" t="s">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AO18">
-        <v>0.99730422320290779</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP18">
-        <v>49.422574613357185</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8498,10 +8498,10 @@
         <v>419</v>
       </c>
       <c r="BC18">
-        <v>0.9932866968373224</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD18">
-        <v>123.07722464908932</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8566,16 +8566,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99505524223378883</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB19">
-        <v>90.653892380538664</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -8602,16 +8602,16 @@
         <v>321</v>
       </c>
       <c r="AM19" t="s">
+        <v>360</v>
+      </c>
+      <c r="AN19" t="s">
         <v>361</v>
       </c>
-      <c r="AN19" t="s">
-        <v>362</v>
-      </c>
       <c r="AO19">
-        <v>0.99805709209211746</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP19">
-        <v>35.619978311179104</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8641,13 +8641,13 @@
         <v>420</v>
       </c>
       <c r="BB19" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="BC19">
-        <v>0.99644388872049838</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD19">
-        <v>65.195373457529499</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8712,16 +8712,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99729953359766199</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB20">
-        <v>49.508550709529651</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8748,16 +8748,16 @@
         <v>323</v>
       </c>
       <c r="AM20" t="s">
+        <v>362</v>
+      </c>
+      <c r="AN20" t="s">
         <v>363</v>
       </c>
-      <c r="AN20" t="s">
-        <v>364</v>
-      </c>
       <c r="AO20">
-        <v>0.99776911581804295</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP20">
-        <v>40.899543335879912</v>
+        <v>28.402000808355538</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8784,16 +8784,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="BB20" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="BC20">
-        <v>0.99399718012600935</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD20">
-        <v>110.05169768982766</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8858,16 +8858,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99860106452186825</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB21">
-        <v>25.647150432415483</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8894,16 +8894,16 @@
         <v>325</v>
       </c>
       <c r="AM21" t="s">
+        <v>364</v>
+      </c>
+      <c r="AN21" t="s">
         <v>365</v>
       </c>
-      <c r="AN21" t="s">
-        <v>366</v>
-      </c>
       <c r="AO21">
-        <v>0.99749126227646956</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP21">
-        <v>45.993524931390482</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8968,16 +8968,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99775856069920277</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB22">
-        <v>41.093053847949164</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -9004,16 +9004,16 @@
         <v>327</v>
       </c>
       <c r="AM22" t="s">
+        <v>366</v>
+      </c>
+      <c r="AN22" t="s">
         <v>367</v>
       </c>
-      <c r="AN22" t="s">
-        <v>368</v>
-      </c>
       <c r="AO22">
-        <v>0.99807543246352515</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP22">
-        <v>35.283738168705199</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9078,16 +9078,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99763459325217896</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB23">
-        <v>43.365790376719588</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9114,16 +9114,16 @@
         <v>329</v>
       </c>
       <c r="AM23" t="s">
+        <v>368</v>
+      </c>
+      <c r="AN23" t="s">
         <v>369</v>
       </c>
-      <c r="AN23" t="s">
-        <v>370</v>
-      </c>
       <c r="AO23">
-        <v>0.99826576737141715</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP23">
-        <v>31.794264857351436</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9188,16 +9188,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99692898913090644</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB24">
-        <v>56.301865933381954</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9224,16 +9224,16 @@
         <v>331</v>
       </c>
       <c r="AM24" t="s">
+        <v>370</v>
+      </c>
+      <c r="AN24" t="s">
         <v>371</v>
       </c>
-      <c r="AN24" t="s">
-        <v>372</v>
-      </c>
       <c r="AO24">
-        <v>0.99871360797890252</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP24">
-        <v>23.583853720120768</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9298,16 +9298,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99738245649758195</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB25">
-        <v>47.988297544331637</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -9334,16 +9334,16 @@
         <v>333</v>
       </c>
       <c r="AM25" t="s">
+        <v>372</v>
+      </c>
+      <c r="AN25" t="s">
         <v>373</v>
       </c>
-      <c r="AN25" t="s">
-        <v>374</v>
-      </c>
       <c r="AO25">
-        <v>0.99641308487583879</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP25">
-        <v>65.760110609622657</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9408,16 +9408,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99648087644372252</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB26">
-        <v>64.517265198419722</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9444,16 +9444,16 @@
         <v>335</v>
       </c>
       <c r="AM26" t="s">
+        <v>374</v>
+      </c>
+      <c r="AN26" t="s">
         <v>375</v>
       </c>
-      <c r="AN26" t="s">
-        <v>376</v>
-      </c>
       <c r="AO26">
-        <v>0.99449756685866841</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP26">
-        <v>100.87794092441324</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9518,16 +9518,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99621535905375425</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB27">
-        <v>69.385084014505708</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9554,16 +9554,16 @@
         <v>337</v>
       </c>
       <c r="AM27" t="s">
+        <v>376</v>
+      </c>
+      <c r="AN27" t="s">
         <v>377</v>
       </c>
-      <c r="AN27" t="s">
-        <v>378</v>
-      </c>
       <c r="AO27">
-        <v>0.99653588726932718</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP27">
-        <v>63.508733395668145</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9628,16 +9628,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99839233674974392</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB28">
-        <v>29.473826254695162</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9664,16 +9664,16 @@
         <v>339</v>
       </c>
       <c r="AM28" t="s">
+        <v>378</v>
+      </c>
+      <c r="AN28" t="s">
         <v>379</v>
       </c>
-      <c r="AN28" t="s">
-        <v>380</v>
-      </c>
       <c r="AO28">
-        <v>0.99635146162488653</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP28">
-        <v>66.889870210414614</v>
+        <v>45.993524931390482</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9738,16 +9738,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99801094175818605</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB29">
-        <v>36.466067766588218</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -9774,16 +9774,16 @@
         <v>341</v>
       </c>
       <c r="AM29" t="s">
+        <v>380</v>
+      </c>
+      <c r="AN29" t="s">
         <v>381</v>
       </c>
-      <c r="AN29" t="s">
-        <v>301</v>
-      </c>
       <c r="AO29">
-        <v>0.99586212495478665</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP29">
-        <v>75.861042495577635</v>
+        <v>35.283738168705199</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9848,16 +9848,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Z30" t="s">
         <v>304</v>
       </c>
       <c r="AA30">
-        <v>0.99909366739195871</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB30">
-        <v>16.616097814091063</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9890,10 +9890,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99622969699231045</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP30">
-        <v>69.122221807641537</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
   </sheetData>
@@ -9902,7 +9902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062937C3-53A2-4D99-BA46-09CCC3F71462}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBEDAC8-2D01-4938-93A1-F960730A9CFD}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10014,7 +10014,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10047,7 +10047,7 @@
         <v>463</v>
       </c>
       <c r="X11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10082,7 +10082,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10115,7 +10115,7 @@
         <v>465</v>
       </c>
       <c r="X12" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10150,7 +10150,7 @@
         <v>427</v>
       </c>
       <c r="K13" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10183,7 +10183,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10251,7 +10251,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10286,7 +10286,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10319,7 +10319,7 @@
         <v>471</v>
       </c>
       <c r="X15" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10354,7 +10354,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10387,7 +10387,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10422,7 +10422,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10455,7 +10455,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10490,7 +10490,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10523,7 +10523,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10558,7 +10558,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10591,7 +10591,7 @@
         <v>479</v>
       </c>
       <c r="X19" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10626,7 +10626,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10659,7 +10659,7 @@
         <v>481</v>
       </c>
       <c r="X20" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10694,7 +10694,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10729,7 +10729,7 @@
         <v>445</v>
       </c>
       <c r="K22" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10764,7 +10764,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10799,7 +10799,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10834,7 +10834,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10869,7 +10869,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10904,7 +10904,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10939,7 +10939,7 @@
         <v>457</v>
       </c>
       <c r="K28" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10974,7 +10974,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -11009,7 +11009,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11024,7 +11024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945D3ECB-43BA-4C90-92A2-B5954FD850F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556EC41C-1886-426B-A713-02C8A1CF5BA7}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14526,7 +14526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC01801-A874-4DF9-B43A-CAF76DE4E8D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{205FA891-2501-4B0C-B6C3-0646030AB617}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15599,7 +15599,7 @@
         <v>576</v>
       </c>
       <c r="C36" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D36" t="s">
         <v>577</v>
@@ -15634,7 +15634,7 @@
         <v>577</v>
       </c>
       <c r="D37" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E37">
         <v>1</v>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75D0CA02-E445-4E25-9666-05FA65CB8FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AFBA5AA-491D-459E-AF22-30A7CA7DFCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -877,6 +877,42 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_004</t>
   </si>
   <si>
@@ -895,90 +931,54 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -994,6 +994,24 @@
     <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
   </si>
   <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
     <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
   </si>
   <si>
@@ -1003,46 +1021,118 @@
     <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
   </si>
   <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+  </si>
+  <si>
     <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
   </si>
   <si>
-    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_011</t>
@@ -1057,40 +1147,16 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_018</t>
@@ -1099,70 +1165,91 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
@@ -1177,37 +1264,16 @@
     <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
@@ -1216,70 +1282,22 @@
     <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w32036484-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_004</t>
@@ -1294,10 +1312,16 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_008</t>
@@ -1312,34 +1336,28 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>e_w175406958-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
@@ -1354,10 +1372,16 @@
     <t>e_PL1-400_POL</t>
   </si>
   <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
@@ -1369,34 +1393,10 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>e_w175406958-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
-  </si>
-  <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
     <t>e_w175406958-400_POL,e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -7160,7 +7160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874DBE8D-DF89-4469-A734-BB13B5240615}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD221FBF-3B29-4FC3-A0D0-F0125757B567}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7440,10 +7440,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99802303154782224</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP11">
-        <v>36.244421623259619</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7476,10 +7476,10 @@
         <v>405</v>
       </c>
       <c r="BC11">
-        <v>0.99255696761939116</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD11">
-        <v>136.4555936444961</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7586,10 +7586,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99714358927215652</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP12">
-        <v>52.367530010463909</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7622,10 +7622,10 @@
         <v>407</v>
       </c>
       <c r="BC12">
-        <v>0.99615776238359954</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD12">
-        <v>70.441022967342263</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7729,13 +7729,13 @@
         <v>349</v>
       </c>
       <c r="AN13" t="s">
-        <v>350</v>
+        <v>292</v>
       </c>
       <c r="AO13">
-        <v>0.99776911581804295</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP13">
-        <v>40.899543335879912</v>
+        <v>75.861042495577635</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7768,10 +7768,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.99603343715055259</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD13">
-        <v>72.720318906536249</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7836,16 +7836,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99812712894455979</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB14">
-        <v>34.335969349736395</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7872,16 +7872,16 @@
         <v>311</v>
       </c>
       <c r="AM14" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN14" t="s">
         <v>351</v>
       </c>
-      <c r="AN14" t="s">
-        <v>352</v>
-      </c>
       <c r="AO14">
-        <v>0.99641308487583879</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP14">
-        <v>65.760110609622657</v>
+        <v>21.284626546395259</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7914,10 +7914,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99383395234396599</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD14">
-        <v>113.04420702728957</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7982,16 +7982,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99834158364926728</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB15">
-        <v>30.404299763434018</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -8018,16 +8018,16 @@
         <v>313</v>
       </c>
       <c r="AM15" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN15" t="s">
         <v>353</v>
       </c>
-      <c r="AN15" t="s">
-        <v>354</v>
-      </c>
       <c r="AO15">
-        <v>0.99449756685866841</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP15">
-        <v>100.87794092441324</v>
+        <v>87.636166232768815</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8060,10 +8060,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99564789206089888</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD15">
-        <v>79.788645550187297</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8128,16 +8128,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.9987403722896917</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB16">
-        <v>23.093174688985375</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8164,16 +8164,16 @@
         <v>315</v>
       </c>
       <c r="AM16" t="s">
+        <v>354</v>
+      </c>
+      <c r="AN16" t="s">
         <v>355</v>
       </c>
-      <c r="AN16" t="s">
-        <v>356</v>
-      </c>
       <c r="AO16">
-        <v>0.99873239758997023</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP16">
-        <v>23.239377517213022</v>
+        <v>63.508733395668145</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8206,10 +8206,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99609037037675463</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD16">
-        <v>71.676543092831025</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8274,16 +8274,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99692898913090644</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB17">
-        <v>56.301865933381954</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -8310,16 +8310,16 @@
         <v>317</v>
       </c>
       <c r="AM17" t="s">
+        <v>356</v>
+      </c>
+      <c r="AN17" t="s">
         <v>357</v>
       </c>
-      <c r="AN17" t="s">
-        <v>358</v>
-      </c>
       <c r="AO17">
-        <v>0.99635146162488653</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP17">
-        <v>66.889870210414614</v>
+        <v>31.794264857351436</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8352,10 +8352,10 @@
         <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.99353710926584593</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD17">
-        <v>118.48633012615811</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8420,16 +8420,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.99511607748745434</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB18">
-        <v>89.538579396670116</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -8456,16 +8456,16 @@
         <v>319</v>
       </c>
       <c r="AM18" t="s">
+        <v>358</v>
+      </c>
+      <c r="AN18" t="s">
         <v>359</v>
       </c>
-      <c r="AN18" t="s">
-        <v>300</v>
-      </c>
       <c r="AO18">
-        <v>0.99586212495478665</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP18">
-        <v>75.861042495577635</v>
+        <v>23.583853720120768</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8498,10 +8498,10 @@
         <v>419</v>
       </c>
       <c r="BC18">
-        <v>0.99399718012600935</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD18">
-        <v>110.05169768982766</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8566,16 +8566,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99763459325217896</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB19">
-        <v>43.365790376719588</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -8608,10 +8608,10 @@
         <v>361</v>
       </c>
       <c r="AO19">
-        <v>0.99622969699231045</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP19">
-        <v>69.122221807641537</v>
+        <v>49.422574613357185</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8641,13 +8641,13 @@
         <v>420</v>
       </c>
       <c r="BB19" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BC19">
-        <v>0.9932866968373224</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD19">
-        <v>123.07722464908932</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8712,16 +8712,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99860106452186825</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB20">
-        <v>25.647150432415483</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8754,10 +8754,10 @@
         <v>363</v>
       </c>
       <c r="AO20">
-        <v>0.99845079995590791</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP20">
-        <v>28.402000808355538</v>
+        <v>35.619978311179104</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8784,16 +8784,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
+        <v>421</v>
+      </c>
+      <c r="BB20" t="s">
         <v>422</v>
       </c>
-      <c r="BB20" t="s">
-        <v>413</v>
-      </c>
       <c r="BC20">
-        <v>0.99644388872049838</v>
+        <v>0.99399718012600935</v>
       </c>
       <c r="BD20">
-        <v>65.195373457529499</v>
+        <v>110.05169768982766</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8858,16 +8858,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99775856069920277</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB21">
-        <v>41.093053847949164</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8900,10 +8900,10 @@
         <v>365</v>
       </c>
       <c r="AO21">
-        <v>0.9963019969989696</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP21">
-        <v>67.796721685557472</v>
+        <v>65.760110609622657</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8968,16 +8968,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.99505524223378883</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB22">
-        <v>90.653892380538664</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -9010,10 +9010,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99826576737141715</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP22">
-        <v>31.794264857351436</v>
+        <v>100.87794092441324</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9078,16 +9078,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99738245649758195</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB23">
-        <v>47.988297544331637</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9120,10 +9120,10 @@
         <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99871360797890252</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP23">
-        <v>23.583853720120768</v>
+        <v>28.402000808355538</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9188,16 +9188,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99729953359766199</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB24">
-        <v>49.508550709529651</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9230,10 +9230,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99730422320290779</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP24">
-        <v>49.422574613357185</v>
+        <v>67.796721685557472</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9298,16 +9298,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99648087644372252</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB25">
-        <v>64.517265198419722</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -9340,10 +9340,10 @@
         <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.99805709209211746</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP25">
-        <v>35.619978311179104</v>
+        <v>40.899543335879912</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9408,16 +9408,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99621535905375425</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB26">
-        <v>69.385084014505708</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9450,10 +9450,10 @@
         <v>375</v>
       </c>
       <c r="AO26">
-        <v>0.99883902037019667</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP26">
-        <v>21.284626546395259</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9518,16 +9518,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99801094175818605</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB27">
-        <v>36.466067766588218</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9560,10 +9560,10 @@
         <v>377</v>
       </c>
       <c r="AO27">
-        <v>0.99521984547821263</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP27">
-        <v>87.636166232768815</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9628,16 +9628,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99909366739195871</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB28">
-        <v>16.616097814091063</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9738,16 +9738,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99572127940552169</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB29">
-        <v>78.443210898768598</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -9848,16 +9848,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Z30" t="s">
         <v>304</v>
       </c>
       <c r="AA30">
-        <v>0.99839233674974392</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB30">
-        <v>29.473826254695162</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9890,10 +9890,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99653588726932718</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP30">
-        <v>63.508733395668145</v>
+        <v>69.122221807641537</v>
       </c>
     </row>
   </sheetData>
@@ -9902,7 +9902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBEDAC8-2D01-4938-93A1-F960730A9CFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA04E66F-EC3B-4029-AC28-E3A39D910DC3}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10014,7 +10014,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10047,7 +10047,7 @@
         <v>463</v>
       </c>
       <c r="X11" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10082,7 +10082,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10115,7 +10115,7 @@
         <v>465</v>
       </c>
       <c r="X12" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10183,7 +10183,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10251,7 +10251,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10286,7 +10286,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10319,7 +10319,7 @@
         <v>471</v>
       </c>
       <c r="X15" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10354,7 +10354,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10387,7 +10387,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10422,7 +10422,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10455,7 +10455,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10490,7 +10490,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10523,7 +10523,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10558,7 +10558,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10591,7 +10591,7 @@
         <v>479</v>
       </c>
       <c r="X19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -10626,7 +10626,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10659,7 +10659,7 @@
         <v>481</v>
       </c>
       <c r="X20" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10694,7 +10694,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10764,7 +10764,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10799,7 +10799,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10834,7 +10834,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10869,7 +10869,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10904,7 +10904,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10939,7 +10939,7 @@
         <v>457</v>
       </c>
       <c r="K28" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10974,7 +10974,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -11009,7 +11009,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11024,7 +11024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556EC41C-1886-426B-A713-02C8A1CF5BA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0E8BD3-674E-4FD9-B03B-D37DEE656B5F}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14526,7 +14526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{205FA891-2501-4B0C-B6C3-0646030AB617}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904B39ED-F08F-40AD-AC13-E0D210BEA885}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15599,7 +15599,7 @@
         <v>576</v>
       </c>
       <c r="C36" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D36" t="s">
         <v>577</v>
@@ -15634,7 +15634,7 @@
         <v>577</v>
       </c>
       <c r="D37" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E37">
         <v>1</v>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AFBA5AA-491D-459E-AF22-30A7CA7DFCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E29EFB6-6A66-4CC3-AD7E-EE114402D970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,18 +853,54 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -877,6 +913,60 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_015</t>
   </si>
   <si>
@@ -889,102 +979,30 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
+  </si>
+  <si>
+    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
+    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+  </si>
+  <si>
     <t>e_PL40-220_POL,e_w158232924-220_POL,e_w178756295-220_POL,e_w111615226-400_POL,e_PL30-220_POL</t>
   </si>
   <si>
@@ -994,55 +1012,55 @@
     <t>e_w254235846-400_POL,e_w173582810-400_POL,e_w255973806-220_POL,e_w88544449-220_POL,e_w255972397-400_POL</t>
   </si>
   <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
+  </si>
+  <si>
+    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
+  </si>
+  <si>
+    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
+  </si>
+  <si>
     <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL,e_w241842600-400_POL,e_PL35-220_POL,e_w199098050-220_POL</t>
   </si>
   <si>
     <t>e_w199098050-220_POL,e_w145037309-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_PL32-220_POL</t>
   </si>
   <si>
-    <t>e_w303870256-400_POL,e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w144646702-400_POL,e_w101914781-220_POL,e_w101914781-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w726776987-220_POL,e_w170368942-220_POL,e_w148060965-400_POL,e_w173613665-220_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL,e_w32036484-220_POL,e_w238640596-220_POL,e_w175406958-220_POL,e_w32036484-400_POL,e_w238640596-400_POL,e_w254938713-400_POL,e_w255293400-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL,e_PL10-400_POL,e_PL4-220_POL,e_w668348943-220_POL,e_w385539724-220_POL,e_PL8-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180542657-220_POL,e_w180535363-220_POL,e_PL46-220_POL,e_w154510504-400_POL,e_w148197330-220_POL,e_PL36-400_POL,e_w79033485-400_POL,e_w255293403-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL22-220_POL,e_PL15-400_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w135598292-220_POL,e_w66051759-220_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w166710856-400_POL,e_PL61-220_POL</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w29115701-220_POL,e_w91384044-400_POL,e_PL20-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_w171383831-220_POL,e_w35366436-220_POL,e_PL21-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255972397-400_POL,e_PL27-400_POL,e_PL17-400_POL,e_w194903381-400_POL,e_w293489663-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255293400-220_POL,e_w46235456-400_POL,e_w385118244-400_POL,e_w46092396-400_POL,e_PL3-220_POL,e_w112614319-400_POL,e_PL6-220_POL</t>
-  </si>
-  <si>
-    <t>e_w175406958-220_POL,e_w175406958-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w534238983-400_POL,e_r18085709-400_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL,e_w191352746-220_POL,e_PL62-400_POL,e_w198635989-220_POL,e_w170368942-220_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w170259740-220_POL</t>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_019</t>
@@ -1051,6 +1069,36 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_009</t>
   </si>
   <si>
@@ -1063,6 +1111,24 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_013</t>
   </si>
   <si>
@@ -1075,24 +1141,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_014</t>
   </si>
   <si>
@@ -1105,36 +1153,6 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_011</t>
   </si>
   <si>
@@ -1147,22 +1165,22 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
@@ -1171,6 +1189,36 @@
     <t>e_w135598292-220_POL,e_w66051759-220_POL,e_w241842600-400_POL,e_w115801644-220_POL,e_w87667718-220_POL,e_w199098050-220_POL</t>
   </si>
   <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
@@ -1180,6 +1228,24 @@
     <t>elc_won_POL_004</t>
   </si>
   <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
+  </si>
+  <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
@@ -1192,24 +1258,6 @@
     <t>e_w101914781-220_POL,e_w101914781-400_POL,e_w101915790-220_POL,e_w303870256-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>e_w145037309-220_POL,e_w144646702-400_POL,e_w101914781-220_POL,e_w91384044-400_POL,e_PL24-220_POL,e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>e_w255293403-400_POL,e_w255284259-220_POL,e_PL22-220_POL,e_PL15-400_POL,e_w171383831-220_POL,e_w72879943-220_POL,e_w143484238-220_POL,e_PL21-220_POL,e_w658600169-400_POL,e_w144646702-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>e_PL35-220_POL,e_w35366436-220_POL,e_w199098050-220_POL,e_w145037309-220_POL,e_PL32-220_POL,e_w29115701-220_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
@@ -1222,36 +1270,6 @@
     <t>e_w185459155-220_POL,e_w336990960-220_POL,e_PL36-400_POL,e_w184899160-220_POL,e_w293489607-400_POL,e_PL41-400_POL,e_w171917072-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>e_w98634956-220_POL,e_w98611253-220_POL,e_w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>e_PL62-400_POL,e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>e_PL61-220_POL,e_w228154083-220_POL,e_w189851841-220_POL,e_w191352746-220_POL,e_w254235846-400_POL,e_w173582810-400_POL,e_w726776987-220_POL,e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL,e_w121656686-400_POL,e_w255972326-400_POL,e_w303870256-400_POL,e_w170259740-220_POL,e_PL17-400_POL,e_w293489663-400_POL,e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>e_w166710856-400_POL,e_w166838338-400_POL</t>
-  </si>
-  <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
@@ -1264,22 +1282,16 @@
     <t>e_PL4-220_POL,e_w668348943-220_POL,e_PL8-220_POL,e_w175406958-220_POL,e_w175406958-400_POL,e_w238640596-400_POL,e_w178838661-220_POL,e_w255314292_POL,e_w255293400-220_POL,e_w534238983-400_POL,e_r18085709-400_POL,e_w46235456-400_POL,e_w385118244-400_POL</t>
   </si>
   <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL,e_PL18-400_POL,e_PL10-400_POL,e_PL30-220_POL,e_w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>e_w255973806-220_POL,e_PL20-220_POL,e_w88544449-220_POL,e_w255972397-400_POL,e_w148060965-400_POL,e_PL27-400_POL,e_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>e_w178756295-220_POL,e_w177749653-220_POL,e_w179279860-220_POL,e_PL46-220_POL,e_w336990960-220_POL,e_w255277953-400_POL,e_PL36-400_POL</t>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_007</t>
@@ -1288,6 +1300,30 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_010</t>
   </si>
   <si>
@@ -1300,54 +1336,51 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>e_w112614319-400_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
     <t>e_w175406958-220_POL,e_w175406958-400_POL</t>
   </si>
   <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>e_w255314292_POL,e_PL1-400_POL</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>e_PL1-400_POL</t>
+  </si>
+  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
@@ -1358,39 +1391,6 @@
   </si>
   <si>
     <t>e_w86494356-400_POL,e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL,e_PL1-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>e_PL1-400_POL,e_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>e_w668348943-220_POL,e_w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
@@ -7160,7 +7160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD221FBF-3B29-4FC3-A0D0-F0125757B567}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F313D39-7B5E-4944-960D-E171BA1E2090}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7398,16 +7398,16 @@
         <v>241</v>
       </c>
       <c r="Y11" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Z11" t="s">
         <v>285</v>
       </c>
       <c r="AA11">
-        <v>0.99733507264559695</v>
+        <v>0.99738245649758195</v>
       </c>
       <c r="AB11">
-        <v>48.857001497390002</v>
+        <v>47.988297544331637</v>
       </c>
       <c r="AD11" t="s">
         <v>240</v>
@@ -7440,10 +7440,10 @@
         <v>346</v>
       </c>
       <c r="AO11">
-        <v>0.99873239758997023</v>
+        <v>0.99641308487583879</v>
       </c>
       <c r="AP11">
-        <v>23.239377517213022</v>
+        <v>65.760110609622657</v>
       </c>
       <c r="AR11" t="s">
         <v>240</v>
@@ -7476,10 +7476,10 @@
         <v>405</v>
       </c>
       <c r="BC11">
-        <v>0.99603343715055259</v>
+        <v>0.9932866968373224</v>
       </c>
       <c r="BD11">
-        <v>72.720318906536249</v>
+        <v>123.07722464908932</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7544,16 +7544,16 @@
         <v>245</v>
       </c>
       <c r="Y12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Z12" t="s">
         <v>286</v>
       </c>
       <c r="AA12">
-        <v>0.99583365539385327</v>
+        <v>0.99648087644372252</v>
       </c>
       <c r="AB12">
-        <v>76.382984446022675</v>
+        <v>64.517265198419722</v>
       </c>
       <c r="AD12" t="s">
         <v>240</v>
@@ -7586,10 +7586,10 @@
         <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99635146162488653</v>
+        <v>0.99449756685866841</v>
       </c>
       <c r="AP12">
-        <v>66.889870210414614</v>
+        <v>100.87794092441324</v>
       </c>
       <c r="AR12" t="s">
         <v>240</v>
@@ -7622,10 +7622,10 @@
         <v>407</v>
       </c>
       <c r="BC12">
-        <v>0.99609037037675463</v>
+        <v>0.99644388872049838</v>
       </c>
       <c r="BD12">
-        <v>71.676543092831025</v>
+        <v>65.195373457529499</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7690,16 +7690,16 @@
         <v>247</v>
       </c>
       <c r="Y13" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="Z13" t="s">
         <v>287</v>
       </c>
       <c r="AA13">
-        <v>0.99875154162789404</v>
+        <v>0.99621535905375425</v>
       </c>
       <c r="AB13">
-        <v>22.888403488609324</v>
+        <v>69.385084014505708</v>
       </c>
       <c r="AD13" t="s">
         <v>240</v>
@@ -7729,13 +7729,13 @@
         <v>349</v>
       </c>
       <c r="AN13" t="s">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="AO13">
-        <v>0.99586212495478665</v>
+        <v>0.99776911581804295</v>
       </c>
       <c r="AP13">
-        <v>75.861042495577635</v>
+        <v>40.899543335879912</v>
       </c>
       <c r="AR13" t="s">
         <v>240</v>
@@ -7768,10 +7768,10 @@
         <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.99353710926584593</v>
+        <v>0.99603343715055259</v>
       </c>
       <c r="BD13">
-        <v>118.48633012615811</v>
+        <v>72.720318906536249</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7836,16 +7836,16 @@
         <v>249</v>
       </c>
       <c r="Y14" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="Z14" t="s">
         <v>288</v>
       </c>
       <c r="AA14">
-        <v>0.99860106452186825</v>
+        <v>0.99511607748745434</v>
       </c>
       <c r="AB14">
-        <v>25.647150432415483</v>
+        <v>89.538579396670116</v>
       </c>
       <c r="AD14" t="s">
         <v>240</v>
@@ -7872,16 +7872,16 @@
         <v>311</v>
       </c>
       <c r="AM14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO14">
-        <v>0.99883902037019667</v>
+        <v>0.99873239758997023</v>
       </c>
       <c r="AP14">
-        <v>21.284626546395259</v>
+        <v>23.239377517213022</v>
       </c>
       <c r="AR14" t="s">
         <v>240</v>
@@ -7914,10 +7914,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99255696761939116</v>
+        <v>0.99383395234396599</v>
       </c>
       <c r="BD14">
-        <v>136.4555936444961</v>
+        <v>113.04420702728957</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7982,16 +7982,16 @@
         <v>251</v>
       </c>
       <c r="Y15" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="Z15" t="s">
         <v>289</v>
       </c>
       <c r="AA15">
-        <v>0.99775856069920277</v>
+        <v>0.99572127940552169</v>
       </c>
       <c r="AB15">
-        <v>41.093053847949164</v>
+        <v>78.443210898768598</v>
       </c>
       <c r="AD15" t="s">
         <v>240</v>
@@ -8018,16 +8018,16 @@
         <v>313</v>
       </c>
       <c r="AM15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO15">
-        <v>0.99521984547821263</v>
+        <v>0.99749126227646956</v>
       </c>
       <c r="AP15">
-        <v>87.636166232768815</v>
+        <v>45.993524931390482</v>
       </c>
       <c r="AR15" t="s">
         <v>240</v>
@@ -8057,13 +8057,13 @@
         <v>412</v>
       </c>
       <c r="BB15" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="BC15">
-        <v>0.99615776238359954</v>
+        <v>0.99564789206089888</v>
       </c>
       <c r="BD15">
-        <v>70.441022967342263</v>
+        <v>79.788645550187297</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8128,16 +8128,16 @@
         <v>253</v>
       </c>
       <c r="Y16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z16" t="s">
         <v>290</v>
       </c>
       <c r="AA16">
-        <v>0.99511607748745434</v>
+        <v>0.99692898913090644</v>
       </c>
       <c r="AB16">
-        <v>89.538579396670116</v>
+        <v>56.301865933381954</v>
       </c>
       <c r="AD16" t="s">
         <v>240</v>
@@ -8164,16 +8164,16 @@
         <v>315</v>
       </c>
       <c r="AM16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO16">
-        <v>0.99653588726932718</v>
+        <v>0.99807543246352515</v>
       </c>
       <c r="AP16">
-        <v>63.508733395668145</v>
+        <v>35.283738168705199</v>
       </c>
       <c r="AR16" t="s">
         <v>240</v>
@@ -8200,16 +8200,16 @@
         <v>394</v>
       </c>
       <c r="BA16" t="s">
+        <v>413</v>
+      </c>
+      <c r="BB16" t="s">
         <v>414</v>
       </c>
-      <c r="BB16" t="s">
-        <v>415</v>
-      </c>
       <c r="BC16">
-        <v>0.9932866968373224</v>
+        <v>0.99255696761939116</v>
       </c>
       <c r="BD16">
-        <v>123.07722464908932</v>
+        <v>136.4555936444961</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8274,16 +8274,16 @@
         <v>255</v>
       </c>
       <c r="Y17" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Z17" t="s">
         <v>291</v>
       </c>
       <c r="AA17">
-        <v>0.99648087644372252</v>
+        <v>0.99733507264559695</v>
       </c>
       <c r="AB17">
-        <v>64.517265198419722</v>
+        <v>48.857001497390002</v>
       </c>
       <c r="AD17" t="s">
         <v>240</v>
@@ -8310,16 +8310,16 @@
         <v>317</v>
       </c>
       <c r="AM17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO17">
-        <v>0.99826576737141715</v>
+        <v>0.99622969699231045</v>
       </c>
       <c r="AP17">
-        <v>31.794264857351436</v>
+        <v>69.122221807641537</v>
       </c>
       <c r="AR17" t="s">
         <v>240</v>
@@ -8346,16 +8346,16 @@
         <v>396</v>
       </c>
       <c r="BA17" t="s">
+        <v>415</v>
+      </c>
+      <c r="BB17" t="s">
         <v>416</v>
       </c>
-      <c r="BB17" t="s">
-        <v>417</v>
-      </c>
       <c r="BC17">
-        <v>0.99644388872049838</v>
+        <v>0.99615776238359954</v>
       </c>
       <c r="BD17">
-        <v>65.195373457529499</v>
+        <v>70.441022967342263</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8420,16 +8420,16 @@
         <v>257</v>
       </c>
       <c r="Y18" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="Z18" t="s">
         <v>292</v>
       </c>
       <c r="AA18">
-        <v>0.99621535905375425</v>
+        <v>0.99583365539385327</v>
       </c>
       <c r="AB18">
-        <v>69.385084014505708</v>
+        <v>76.382984446022675</v>
       </c>
       <c r="AD18" t="s">
         <v>240</v>
@@ -8456,16 +8456,16 @@
         <v>319</v>
       </c>
       <c r="AM18" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO18">
-        <v>0.99871360797890252</v>
+        <v>0.99845079995590791</v>
       </c>
       <c r="AP18">
-        <v>23.583853720120768</v>
+        <v>28.402000808355538</v>
       </c>
       <c r="AR18" t="s">
         <v>240</v>
@@ -8492,16 +8492,16 @@
         <v>398</v>
       </c>
       <c r="BA18" t="s">
+        <v>417</v>
+      </c>
+      <c r="BB18" t="s">
         <v>418</v>
       </c>
-      <c r="BB18" t="s">
-        <v>419</v>
-      </c>
       <c r="BC18">
-        <v>0.99383395234396599</v>
+        <v>0.99609037037675463</v>
       </c>
       <c r="BD18">
-        <v>113.04420702728957</v>
+        <v>71.676543092831025</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8566,16 +8566,16 @@
         <v>259</v>
       </c>
       <c r="Y19" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="Z19" t="s">
         <v>293</v>
       </c>
       <c r="AA19">
-        <v>0.99729953359766199</v>
+        <v>0.99875154162789404</v>
       </c>
       <c r="AB19">
-        <v>49.508550709529651</v>
+        <v>22.888403488609324</v>
       </c>
       <c r="AD19" t="s">
         <v>240</v>
@@ -8602,16 +8602,16 @@
         <v>321</v>
       </c>
       <c r="AM19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO19">
-        <v>0.99730422320290779</v>
+        <v>0.9963019969989696</v>
       </c>
       <c r="AP19">
-        <v>49.422574613357185</v>
+        <v>67.796721685557472</v>
       </c>
       <c r="AR19" t="s">
         <v>240</v>
@@ -8638,16 +8638,16 @@
         <v>400</v>
       </c>
       <c r="BA19" t="s">
+        <v>419</v>
+      </c>
+      <c r="BB19" t="s">
         <v>420</v>
       </c>
-      <c r="BB19" t="s">
-        <v>417</v>
-      </c>
       <c r="BC19">
-        <v>0.99564789206089888</v>
+        <v>0.99353710926584593</v>
       </c>
       <c r="BD19">
-        <v>79.788645550187297</v>
+        <v>118.48633012615811</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8712,16 +8712,16 @@
         <v>261</v>
       </c>
       <c r="Y20" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="Z20" t="s">
         <v>294</v>
       </c>
       <c r="AA20">
-        <v>0.99812712894455979</v>
+        <v>0.99801094175818605</v>
       </c>
       <c r="AB20">
-        <v>34.335969349736395</v>
+        <v>36.466067766588218</v>
       </c>
       <c r="AD20" t="s">
         <v>240</v>
@@ -8748,16 +8748,16 @@
         <v>323</v>
       </c>
       <c r="AM20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO20">
-        <v>0.99805709209211746</v>
+        <v>0.99635146162488653</v>
       </c>
       <c r="AP20">
-        <v>35.619978311179104</v>
+        <v>66.889870210414614</v>
       </c>
       <c r="AR20" t="s">
         <v>240</v>
@@ -8858,16 +8858,16 @@
         <v>263</v>
       </c>
       <c r="Y21" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="Z21" t="s">
         <v>295</v>
       </c>
       <c r="AA21">
-        <v>0.99834158364926728</v>
+        <v>0.99909366739195871</v>
       </c>
       <c r="AB21">
-        <v>30.404299763434018</v>
+        <v>16.616097814091063</v>
       </c>
       <c r="AD21" t="s">
         <v>240</v>
@@ -8894,16 +8894,16 @@
         <v>325</v>
       </c>
       <c r="AM21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN21" t="s">
-        <v>365</v>
+        <v>287</v>
       </c>
       <c r="AO21">
-        <v>0.99641308487583879</v>
+        <v>0.99586212495478665</v>
       </c>
       <c r="AP21">
-        <v>65.760110609622657</v>
+        <v>75.861042495577635</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8968,16 +8968,16 @@
         <v>265</v>
       </c>
       <c r="Y22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z22" t="s">
         <v>296</v>
       </c>
       <c r="AA22">
-        <v>0.9987403722896917</v>
+        <v>0.99839233674974392</v>
       </c>
       <c r="AB22">
-        <v>23.093174688985375</v>
+        <v>29.473826254695162</v>
       </c>
       <c r="AD22" t="s">
         <v>240</v>
@@ -9010,10 +9010,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99449756685866841</v>
+        <v>0.99653588726932718</v>
       </c>
       <c r="AP22">
-        <v>100.87794092441324</v>
+        <v>63.508733395668145</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9078,16 +9078,16 @@
         <v>267</v>
       </c>
       <c r="Y23" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="Z23" t="s">
         <v>297</v>
       </c>
       <c r="AA23">
-        <v>0.99801094175818605</v>
+        <v>0.99729953359766199</v>
       </c>
       <c r="AB23">
-        <v>36.466067766588218</v>
+        <v>49.508550709529651</v>
       </c>
       <c r="AD23" t="s">
         <v>240</v>
@@ -9120,10 +9120,10 @@
         <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99845079995590791</v>
+        <v>0.99826576737141715</v>
       </c>
       <c r="AP23">
-        <v>28.402000808355538</v>
+        <v>31.794264857351436</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9188,16 +9188,16 @@
         <v>269</v>
       </c>
       <c r="Y24" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="Z24" t="s">
         <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99909366739195871</v>
+        <v>0.99812712894455979</v>
       </c>
       <c r="AB24">
-        <v>16.616097814091063</v>
+        <v>34.335969349736395</v>
       </c>
       <c r="AD24" t="s">
         <v>240</v>
@@ -9230,10 +9230,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.9963019969989696</v>
+        <v>0.99871360797890252</v>
       </c>
       <c r="AP24">
-        <v>67.796721685557472</v>
+        <v>23.583853720120768</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9298,16 +9298,16 @@
         <v>271</v>
       </c>
       <c r="Y25" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="Z25" t="s">
         <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.99839233674974392</v>
+        <v>0.99834158364926728</v>
       </c>
       <c r="AB25">
-        <v>29.473826254695162</v>
+        <v>30.404299763434018</v>
       </c>
       <c r="AD25" t="s">
         <v>240</v>
@@ -9340,10 +9340,10 @@
         <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.99776911581804295</v>
+        <v>0.99883902037019667</v>
       </c>
       <c r="AP25">
-        <v>40.899543335879912</v>
+        <v>21.284626546395259</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9408,16 +9408,16 @@
         <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s">
         <v>300</v>
       </c>
       <c r="AA26">
-        <v>0.99572127940552169</v>
+        <v>0.9987403722896917</v>
       </c>
       <c r="AB26">
-        <v>78.443210898768598</v>
+        <v>23.093174688985375</v>
       </c>
       <c r="AD26" t="s">
         <v>240</v>
@@ -9450,10 +9450,10 @@
         <v>375</v>
       </c>
       <c r="AO26">
-        <v>0.99802303154782224</v>
+        <v>0.99521984547821263</v>
       </c>
       <c r="AP26">
-        <v>36.244421623259619</v>
+        <v>87.636166232768815</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9518,16 +9518,16 @@
         <v>275</v>
       </c>
       <c r="Y27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z27" t="s">
         <v>301</v>
       </c>
       <c r="AA27">
-        <v>0.99738245649758195</v>
+        <v>0.99763459325217896</v>
       </c>
       <c r="AB27">
-        <v>47.988297544331637</v>
+        <v>43.365790376719588</v>
       </c>
       <c r="AD27" t="s">
         <v>240</v>
@@ -9560,10 +9560,10 @@
         <v>377</v>
       </c>
       <c r="AO27">
-        <v>0.99714358927215652</v>
+        <v>0.99730422320290779</v>
       </c>
       <c r="AP27">
-        <v>52.367530010463909</v>
+        <v>49.422574613357185</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9628,16 +9628,16 @@
         <v>277</v>
       </c>
       <c r="Y28" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Z28" t="s">
         <v>302</v>
       </c>
       <c r="AA28">
-        <v>0.99763459325217896</v>
+        <v>0.99505524223378883</v>
       </c>
       <c r="AB28">
-        <v>43.365790376719588</v>
+        <v>90.653892380538664</v>
       </c>
       <c r="AD28" t="s">
         <v>240</v>
@@ -9670,10 +9670,10 @@
         <v>379</v>
       </c>
       <c r="AO28">
-        <v>0.99749126227646956</v>
+        <v>0.99805709209211746</v>
       </c>
       <c r="AP28">
-        <v>45.993524931390482</v>
+        <v>35.619978311179104</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9738,16 +9738,16 @@
         <v>279</v>
       </c>
       <c r="Y29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Z29" t="s">
         <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.99505524223378883</v>
+        <v>0.99860106452186825</v>
       </c>
       <c r="AB29">
-        <v>90.653892380538664</v>
+        <v>25.647150432415483</v>
       </c>
       <c r="AD29" t="s">
         <v>240</v>
@@ -9780,10 +9780,10 @@
         <v>381</v>
       </c>
       <c r="AO29">
-        <v>0.99807543246352515</v>
+        <v>0.99802303154782224</v>
       </c>
       <c r="AP29">
-        <v>35.283738168705199</v>
+        <v>36.244421623259619</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9848,16 +9848,16 @@
         <v>281</v>
       </c>
       <c r="Y30" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="Z30" t="s">
         <v>304</v>
       </c>
       <c r="AA30">
-        <v>0.99692898913090644</v>
+        <v>0.99775856069920277</v>
       </c>
       <c r="AB30">
-        <v>56.301865933381954</v>
+        <v>41.093053847949164</v>
       </c>
       <c r="AD30" t="s">
         <v>240</v>
@@ -9890,10 +9890,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99622969699231045</v>
+        <v>0.99714358927215652</v>
       </c>
       <c r="AP30">
-        <v>69.122221807641537</v>
+        <v>52.367530010463909</v>
       </c>
     </row>
   </sheetData>
@@ -9902,7 +9902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA04E66F-EC3B-4029-AC28-E3A39D910DC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2DF36F-B208-4F92-A495-60148317DEFE}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10014,7 +10014,7 @@
         <v>423</v>
       </c>
       <c r="K11" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="L11">
         <v>0.30278350605008381</v>
@@ -10047,7 +10047,7 @@
         <v>463</v>
       </c>
       <c r="X11" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -10082,7 +10082,7 @@
         <v>425</v>
       </c>
       <c r="K12" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="L12">
         <v>0.44035497786033617</v>
@@ -10115,7 +10115,7 @@
         <v>465</v>
       </c>
       <c r="X12" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -10150,7 +10150,7 @@
         <v>427</v>
       </c>
       <c r="K13" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="L13">
         <v>1.6077871713950227</v>
@@ -10183,7 +10183,7 @@
         <v>467</v>
       </c>
       <c r="X13" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -10218,7 +10218,7 @@
         <v>429</v>
       </c>
       <c r="K14" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="L14">
         <v>2.531891424764753</v>
@@ -10251,7 +10251,7 @@
         <v>469</v>
       </c>
       <c r="X14" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -10286,7 +10286,7 @@
         <v>431</v>
       </c>
       <c r="K15" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L15">
         <v>7.6497810049421515</v>
@@ -10319,7 +10319,7 @@
         <v>471</v>
       </c>
       <c r="X15" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -10354,7 +10354,7 @@
         <v>433</v>
       </c>
       <c r="K16" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="L16">
         <v>0.63333325583919986</v>
@@ -10387,7 +10387,7 @@
         <v>473</v>
       </c>
       <c r="X16" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Y16">
         <v>8.8230000000000004</v>
@@ -10422,7 +10422,7 @@
         <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="L17">
         <v>0.78389041837100704</v>
@@ -10455,7 +10455,7 @@
         <v>475</v>
       </c>
       <c r="X17" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -10490,7 +10490,7 @@
         <v>437</v>
       </c>
       <c r="K18" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="L18">
         <v>3.0365724666245324</v>
@@ -10523,7 +10523,7 @@
         <v>477</v>
       </c>
       <c r="X18" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -10558,7 +10558,7 @@
         <v>439</v>
       </c>
       <c r="K19" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="L19">
         <v>0.22970161230087291</v>
@@ -10626,7 +10626,7 @@
         <v>441</v>
       </c>
       <c r="K20" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="L20">
         <v>0.27066515065379043</v>
@@ -10659,7 +10659,7 @@
         <v>481</v>
       </c>
       <c r="X20" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -10694,7 +10694,7 @@
         <v>443</v>
       </c>
       <c r="K21" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="L21">
         <v>0.32193208719379746</v>
@@ -10729,7 +10729,7 @@
         <v>445</v>
       </c>
       <c r="K22" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="L22">
         <v>0.6573344927201471</v>
@@ -10764,7 +10764,7 @@
         <v>447</v>
       </c>
       <c r="K23" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="L23">
         <v>0.28992997651770519</v>
@@ -10799,7 +10799,7 @@
         <v>449</v>
       </c>
       <c r="K24" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="L24">
         <v>0.74609319967150689</v>
@@ -10834,7 +10834,7 @@
         <v>451</v>
       </c>
       <c r="K25" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10869,7 +10869,7 @@
         <v>453</v>
       </c>
       <c r="K26" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="L26">
         <v>0.7924639655878376</v>
@@ -10904,7 +10904,7 @@
         <v>455</v>
       </c>
       <c r="K27" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10939,7 +10939,7 @@
         <v>457</v>
       </c>
       <c r="K28" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="L28">
         <v>1.4327274230737423</v>
@@ -10974,7 +10974,7 @@
         <v>459</v>
       </c>
       <c r="K29" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="L29">
         <v>0.58742801517356968</v>
@@ -11009,7 +11009,7 @@
         <v>461</v>
       </c>
       <c r="K30" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="L30">
         <v>0.35405891742987328</v>
@@ -11024,7 +11024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0E8BD3-674E-4FD9-B03B-D37DEE656B5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5FEA79-DBE7-4722-9963-B0FD82681EC1}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14526,7 +14526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904B39ED-F08F-40AD-AC13-E0D210BEA885}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B63E126-0A6F-4058-BD81-7D35D7CB13D5}">
   <dimension ref="B2:M87"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15599,7 +15599,7 @@
         <v>576</v>
       </c>
       <c r="C36" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="D36" t="s">
         <v>577</v>
@@ -15634,7 +15634,7 @@
         <v>577</v>
       </c>
       <c r="D37" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="E37">
         <v>1</v>
